--- a/research/traditional_assets/database/data/mexico/mexico_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_environmental_waste_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1010704306027203</v>
+        <v>0.1007987193109121</v>
       </c>
       <c r="C2">
-        <v>379.641624105747</v>
+        <v>377.3110300723044</v>
       </c>
       <c r="D2">
-        <v>356.941624105747</v>
+        <v>358.7050300723045</v>
       </c>
       <c r="E2">
-        <v>-166.3</v>
+        <v>-162.206</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.093999999999999</v>
       </c>
       <c r="G2">
         <v>22.7</v>
@@ -1451,28 +1451,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2059282</v>
       </c>
       <c r="N2">
-        <v>52.66666666666667</v>
+        <v>52.46073846666667</v>
       </c>
       <c r="O2">
-        <v>15.8</v>
+        <v>15.73822154</v>
       </c>
       <c r="P2">
-        <v>36.86666666666667</v>
+        <v>36.72251692666667</v>
       </c>
       <c r="Q2">
-        <v>66.86666666666667</v>
+        <v>66.72251692666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1010704306027203</v>
+        <v>0.101461231627184</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8099387413235496</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>255.752571365489</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1007987193109121</v>
+        <v>0.100527008019104</v>
       </c>
       <c r="C3">
-        <v>377.3110300723044</v>
+        <v>374.997946125033</v>
       </c>
       <c r="D3">
-        <v>358.7050300723045</v>
+        <v>360.485946125033</v>
       </c>
       <c r="E3">
-        <v>-162.206</v>
+        <v>-158.112</v>
       </c>
       <c r="F3">
-        <v>4.093999999999999</v>
+        <v>8.187999999999999</v>
       </c>
       <c r="G3">
         <v>22.7</v>
@@ -1533,28 +1533,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M3">
-        <v>0.2059282</v>
+        <v>0.4118563999999999</v>
       </c>
       <c r="N3">
-        <v>52.46073846666667</v>
+        <v>52.25481026666667</v>
       </c>
       <c r="O3">
-        <v>15.73822154</v>
+        <v>15.67644308</v>
       </c>
       <c r="P3">
-        <v>36.72251692666667</v>
+        <v>36.57836718666667</v>
       </c>
       <c r="Q3">
-        <v>66.72251692666667</v>
+        <v>66.57836718666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.101461231627184</v>
+        <v>0.1018600081827592</v>
       </c>
       <c r="T3">
-        <v>0.8099387413235496</v>
+        <v>0.8157414261016235</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>255.752571365489</v>
+        <v>127.8762856827445</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.100527008019104</v>
+        <v>0.1002552967272958</v>
       </c>
       <c r="C4">
-        <v>374.997946125033</v>
+        <v>372.7026343700136</v>
       </c>
       <c r="D4">
-        <v>360.485946125033</v>
+        <v>362.2846343700136</v>
       </c>
       <c r="E4">
-        <v>-158.112</v>
+        <v>-154.018</v>
       </c>
       <c r="F4">
-        <v>8.187999999999999</v>
+        <v>12.282</v>
       </c>
       <c r="G4">
         <v>22.7</v>
@@ -1615,28 +1615,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M4">
-        <v>0.4118563999999999</v>
+        <v>0.6177845999999999</v>
       </c>
       <c r="N4">
-        <v>52.25481026666667</v>
+        <v>52.04888206666667</v>
       </c>
       <c r="O4">
-        <v>15.67644308</v>
+        <v>15.61466462</v>
       </c>
       <c r="P4">
-        <v>36.57836718666667</v>
+        <v>36.43421744666667</v>
       </c>
       <c r="Q4">
-        <v>66.57836718666667</v>
+        <v>66.43421744666668</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1018600081827592</v>
+        <v>0.1022670069353565</v>
       </c>
       <c r="T4">
-        <v>0.8157414261016235</v>
+        <v>0.8216637538648123</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>127.8762856827445</v>
+        <v>85.25085712182964</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1002552967272958</v>
+        <v>0.09998358543548767</v>
       </c>
       <c r="C5">
-        <v>372.7026343700136</v>
+        <v>370.4253621707998</v>
       </c>
       <c r="D5">
-        <v>362.2846343700136</v>
+        <v>364.1013621707997</v>
       </c>
       <c r="E5">
-        <v>-154.018</v>
+        <v>-149.924</v>
       </c>
       <c r="F5">
-        <v>12.282</v>
+        <v>16.376</v>
       </c>
       <c r="G5">
         <v>22.7</v>
@@ -1697,28 +1697,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M5">
-        <v>0.6177845999999999</v>
+        <v>0.8237127999999998</v>
       </c>
       <c r="N5">
-        <v>52.04888206666667</v>
+        <v>51.84295386666667</v>
       </c>
       <c r="O5">
-        <v>15.61466462</v>
+        <v>15.55288616</v>
       </c>
       <c r="P5">
-        <v>36.43421744666667</v>
+        <v>36.29006770666667</v>
       </c>
       <c r="Q5">
-        <v>66.43421744666668</v>
+        <v>66.29006770666666</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1022670069353565</v>
+        <v>0.102682484828633</v>
       </c>
       <c r="T5">
-        <v>0.8216637538648123</v>
+        <v>0.8277094634564007</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>85.25085712182964</v>
+        <v>63.93814284137224</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09998358543548767</v>
+        <v>0.0997118741436795</v>
       </c>
       <c r="C6">
-        <v>370.4253621707998</v>
+        <v>368.166402280904</v>
       </c>
       <c r="D6">
-        <v>364.1013621707997</v>
+        <v>365.936402280904</v>
       </c>
       <c r="E6">
-        <v>-149.924</v>
+        <v>-145.83</v>
       </c>
       <c r="F6">
-        <v>16.376</v>
+        <v>20.47</v>
       </c>
       <c r="G6">
         <v>22.7</v>
@@ -1779,28 +1779,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M6">
-        <v>0.8237127999999998</v>
+        <v>1.029641</v>
       </c>
       <c r="N6">
-        <v>51.84295386666667</v>
+        <v>51.63702566666667</v>
       </c>
       <c r="O6">
-        <v>15.55288616</v>
+        <v>15.4911077</v>
       </c>
       <c r="P6">
-        <v>36.29006770666667</v>
+        <v>36.14591796666667</v>
       </c>
       <c r="Q6">
-        <v>66.29006770666666</v>
+        <v>66.14591796666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.102682484828633</v>
+        <v>0.1031067096249258</v>
       </c>
       <c r="T6">
-        <v>0.8277094634564007</v>
+        <v>0.8338824511446543</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.93814284137224</v>
+        <v>51.15051427309779</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0997118741436795</v>
+        <v>0.09944016285187134</v>
       </c>
       <c r="C7">
-        <v>368.166402280904</v>
+        <v>365.9260329803101</v>
       </c>
       <c r="D7">
-        <v>365.936402280904</v>
+        <v>367.7900329803102</v>
       </c>
       <c r="E7">
-        <v>-145.83</v>
+        <v>-141.736</v>
       </c>
       <c r="F7">
-        <v>20.47</v>
+        <v>24.564</v>
       </c>
       <c r="G7">
         <v>22.7</v>
@@ -1861,28 +1861,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M7">
-        <v>1.029641</v>
+        <v>1.2355692</v>
       </c>
       <c r="N7">
-        <v>51.63702566666667</v>
+        <v>51.43109746666667</v>
       </c>
       <c r="O7">
-        <v>15.4911077</v>
+        <v>15.42932924</v>
       </c>
       <c r="P7">
-        <v>36.14591796666667</v>
+        <v>36.00176822666667</v>
       </c>
       <c r="Q7">
-        <v>66.14591796666667</v>
+        <v>66.00176822666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1031067096249258</v>
+        <v>0.1035399604807142</v>
       </c>
       <c r="T7">
-        <v>0.8338824511446543</v>
+        <v>0.8401867789964877</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.15051427309779</v>
+        <v>42.62542856091481</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09944016285187134</v>
+        <v>0.09916845156006319</v>
       </c>
       <c r="C8">
-        <v>365.9260329803101</v>
+        <v>363.7045382161567</v>
       </c>
       <c r="D8">
-        <v>367.7900329803102</v>
+        <v>369.6625382161567</v>
       </c>
       <c r="E8">
-        <v>-141.736</v>
+        <v>-137.642</v>
       </c>
       <c r="F8">
-        <v>24.564</v>
+        <v>28.65799999999999</v>
       </c>
       <c r="G8">
         <v>22.7</v>
@@ -1943,28 +1943,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M8">
-        <v>1.2355692</v>
+        <v>1.4414974</v>
       </c>
       <c r="N8">
-        <v>51.43109746666667</v>
+        <v>51.22516926666667</v>
       </c>
       <c r="O8">
-        <v>15.42932924</v>
+        <v>15.36755078</v>
       </c>
       <c r="P8">
-        <v>36.00176822666667</v>
+        <v>35.85761848666667</v>
       </c>
       <c r="Q8">
-        <v>66.00176822666667</v>
+        <v>65.85761848666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1035399604807142</v>
+        <v>0.1039825285592077</v>
       </c>
       <c r="T8">
-        <v>0.8401867789964877</v>
+        <v>0.8466266837913715</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.62542856091482</v>
+        <v>36.53608162364128</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09916845156006318</v>
+        <v>0.09889674026825503</v>
       </c>
       <c r="C9">
-        <v>363.7045382161568</v>
+        <v>361.502207747739</v>
       </c>
       <c r="D9">
-        <v>369.6625382161568</v>
+        <v>371.554207747739</v>
       </c>
       <c r="E9">
-        <v>-137.642</v>
+        <v>-133.548</v>
       </c>
       <c r="F9">
-        <v>28.658</v>
+        <v>32.752</v>
       </c>
       <c r="G9">
         <v>22.7</v>
@@ -2025,28 +2025,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M9">
-        <v>1.4414974</v>
+        <v>1.6474256</v>
       </c>
       <c r="N9">
-        <v>51.22516926666667</v>
+        <v>51.01924106666667</v>
       </c>
       <c r="O9">
-        <v>15.36755078</v>
+        <v>15.30577232</v>
       </c>
       <c r="P9">
-        <v>35.85761848666667</v>
+        <v>35.71346874666667</v>
       </c>
       <c r="Q9">
-        <v>65.85761848666667</v>
+        <v>65.71346874666668</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1039825285592077</v>
+        <v>0.1044347176828859</v>
       </c>
       <c r="T9">
-        <v>0.8466266837913715</v>
+        <v>0.8532065865165788</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.53608162364127</v>
+        <v>31.96907142068612</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09889674026825503</v>
+        <v>0.09862502897644687</v>
       </c>
       <c r="C10">
-        <v>361.502207747739</v>
+        <v>359.3193372959861</v>
       </c>
       <c r="D10">
-        <v>371.554207747739</v>
+        <v>373.4653372959861</v>
       </c>
       <c r="E10">
-        <v>-133.548</v>
+        <v>-129.454</v>
       </c>
       <c r="F10">
-        <v>32.752</v>
+        <v>36.846</v>
       </c>
       <c r="G10">
         <v>22.7</v>
@@ -2107,28 +2107,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M10">
-        <v>1.6474256</v>
+        <v>1.8533538</v>
       </c>
       <c r="N10">
-        <v>51.01924106666667</v>
+        <v>50.81331286666667</v>
       </c>
       <c r="O10">
-        <v>15.30577232</v>
+        <v>15.24399386</v>
       </c>
       <c r="P10">
-        <v>35.71346874666667</v>
+        <v>35.56931900666667</v>
       </c>
       <c r="Q10">
-        <v>65.71346874666668</v>
+        <v>65.56931900666667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1044347176828859</v>
+        <v>0.1048968450290625</v>
       </c>
       <c r="T10">
-        <v>0.8532065865165788</v>
+        <v>0.8599311024884937</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.96907142068612</v>
+        <v>28.41695237394321</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09862502897644687</v>
+        <v>0.0983533176846387</v>
       </c>
       <c r="C11">
-        <v>359.3193372959861</v>
+        <v>357.1562286975755</v>
       </c>
       <c r="D11">
-        <v>373.4653372959861</v>
+        <v>375.3962286975755</v>
       </c>
       <c r="E11">
-        <v>-129.454</v>
+        <v>-125.36</v>
       </c>
       <c r="F11">
-        <v>36.846</v>
+        <v>40.94</v>
       </c>
       <c r="G11">
         <v>22.7</v>
@@ -2189,28 +2189,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M11">
-        <v>1.8533538</v>
+        <v>2.059282</v>
       </c>
       <c r="N11">
-        <v>50.81331286666667</v>
+        <v>50.60738466666668</v>
       </c>
       <c r="O11">
-        <v>15.24399386</v>
+        <v>15.1822154</v>
       </c>
       <c r="P11">
-        <v>35.56931900666667</v>
+        <v>35.42516926666667</v>
       </c>
       <c r="Q11">
-        <v>65.56931900666667</v>
+        <v>65.42516926666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1048968450290625</v>
+        <v>0.1053692418718208</v>
       </c>
       <c r="T11">
-        <v>0.8599311024884937</v>
+        <v>0.8668050521486734</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.41695237394321</v>
+        <v>25.5752571365489</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0983533176846387</v>
+        <v>0.09808160639283053</v>
       </c>
       <c r="C12">
-        <v>357.1562286975755</v>
+        <v>355.0131900638529</v>
       </c>
       <c r="D12">
-        <v>375.3962286975755</v>
+        <v>377.3471900638529</v>
       </c>
       <c r="E12">
-        <v>-125.36</v>
+        <v>-121.266</v>
       </c>
       <c r="F12">
-        <v>40.94</v>
+        <v>45.034</v>
       </c>
       <c r="G12">
         <v>22.7</v>
@@ -2271,28 +2271,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M12">
-        <v>2.059282</v>
+        <v>2.2652102</v>
       </c>
       <c r="N12">
-        <v>50.60738466666668</v>
+        <v>50.40145646666667</v>
       </c>
       <c r="O12">
-        <v>15.1822154</v>
+        <v>15.12043694</v>
       </c>
       <c r="P12">
-        <v>35.42516926666667</v>
+        <v>35.28101952666667</v>
       </c>
       <c r="Q12">
-        <v>65.42516926666667</v>
+        <v>65.28101952666667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1053692418718208</v>
+        <v>0.1058522543739669</v>
       </c>
       <c r="T12">
-        <v>0.8668050521486734</v>
+        <v>0.8738334725877337</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.5752571365489</v>
+        <v>23.25023376049899</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09808160639283053</v>
+        <v>0.09780989510102239</v>
       </c>
       <c r="C13">
-        <v>355.0131900638529</v>
+        <v>352.8905359447332</v>
       </c>
       <c r="D13">
-        <v>377.3471900638529</v>
+        <v>379.3185359447332</v>
       </c>
       <c r="E13">
-        <v>-121.266</v>
+        <v>-117.172</v>
       </c>
       <c r="F13">
-        <v>45.034</v>
+        <v>49.12799999999999</v>
       </c>
       <c r="G13">
         <v>22.7</v>
@@ -2353,28 +2353,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M13">
-        <v>2.2652102</v>
+        <v>2.4711384</v>
       </c>
       <c r="N13">
-        <v>50.40145646666667</v>
+        <v>50.19552826666667</v>
       </c>
       <c r="O13">
-        <v>15.12043694</v>
+        <v>15.05865848</v>
       </c>
       <c r="P13">
-        <v>35.28101952666667</v>
+        <v>35.13686978666667</v>
       </c>
       <c r="Q13">
-        <v>65.28101952666667</v>
+        <v>65.13686978666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1058522543739669</v>
+        <v>0.10634624443298</v>
       </c>
       <c r="T13">
-        <v>0.8738334725877337</v>
+        <v>0.8810216298549545</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.25023376049899</v>
+        <v>21.31271428045741</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09780989510102239</v>
+        <v>0.09753818380921422</v>
       </c>
       <c r="C14">
-        <v>352.8905359447332</v>
+        <v>350.7885874977677</v>
       </c>
       <c r="D14">
-        <v>379.3185359447332</v>
+        <v>381.3105874977677</v>
       </c>
       <c r="E14">
-        <v>-117.172</v>
+        <v>-113.078</v>
       </c>
       <c r="F14">
-        <v>49.12799999999999</v>
+        <v>53.222</v>
       </c>
       <c r="G14">
         <v>22.7</v>
@@ -2435,28 +2435,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M14">
-        <v>2.4711384</v>
+        <v>2.6770666</v>
       </c>
       <c r="N14">
-        <v>50.19552826666667</v>
+        <v>49.98960006666667</v>
       </c>
       <c r="O14">
-        <v>15.05865848</v>
+        <v>14.99688002</v>
       </c>
       <c r="P14">
-        <v>35.13686978666667</v>
+        <v>34.99272004666667</v>
       </c>
       <c r="Q14">
-        <v>65.13686978666667</v>
+        <v>64.99272004666668</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.10634624443298</v>
+        <v>0.1068515905853037</v>
       </c>
       <c r="T14">
-        <v>0.8810216298549545</v>
+        <v>0.8883750321168239</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.31271428045741</v>
+        <v>19.67327472042222</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09753818380921422</v>
+        <v>0.09726647251740606</v>
       </c>
       <c r="C15">
-        <v>350.7885874977677</v>
+        <v>348.7076726625633</v>
       </c>
       <c r="D15">
-        <v>381.3105874977677</v>
+        <v>383.3236726625633</v>
       </c>
       <c r="E15">
-        <v>-113.078</v>
+        <v>-108.984</v>
       </c>
       <c r="F15">
-        <v>53.222</v>
+        <v>57.316</v>
       </c>
       <c r="G15">
         <v>22.7</v>
@@ -2517,28 +2517,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M15">
-        <v>2.6770666</v>
+        <v>2.8829948</v>
       </c>
       <c r="N15">
-        <v>49.98960006666667</v>
+        <v>49.78367186666667</v>
       </c>
       <c r="O15">
-        <v>14.99688002</v>
+        <v>14.93510156</v>
       </c>
       <c r="P15">
-        <v>34.99272004666667</v>
+        <v>34.84857030666667</v>
       </c>
       <c r="Q15">
-        <v>64.99272004666668</v>
+        <v>64.84857030666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1068515905853037</v>
+        <v>0.107368688973728</v>
       </c>
       <c r="T15">
-        <v>0.8883750321168239</v>
+        <v>0.8958994437336205</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.67327472042222</v>
+        <v>18.26804081182064</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09726647251740606</v>
+        <v>0.0969947612255979</v>
       </c>
       <c r="C16">
-        <v>348.7076726625633</v>
+        <v>346.6481263407594</v>
       </c>
       <c r="D16">
-        <v>383.3236726625633</v>
+        <v>385.3581263407594</v>
       </c>
       <c r="E16">
-        <v>-108.984</v>
+        <v>-104.89</v>
       </c>
       <c r="F16">
-        <v>57.316</v>
+        <v>61.41</v>
       </c>
       <c r="G16">
         <v>22.7</v>
@@ -2599,28 +2599,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M16">
-        <v>2.8829948</v>
+        <v>3.088923</v>
       </c>
       <c r="N16">
-        <v>49.78367186666667</v>
+        <v>49.57774366666667</v>
       </c>
       <c r="O16">
-        <v>14.93510156</v>
+        <v>14.8733231</v>
       </c>
       <c r="P16">
-        <v>34.84857030666667</v>
+        <v>34.70442056666667</v>
       </c>
       <c r="Q16">
-        <v>64.84857030666667</v>
+        <v>64.70442056666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.107368688973728</v>
+        <v>0.1078979543830564</v>
       </c>
       <c r="T16">
-        <v>0.8958994437336205</v>
+        <v>0.903600900329636</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.26804081182064</v>
+        <v>17.05017142436593</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0969947612255979</v>
+        <v>0.09672304993378975</v>
       </c>
       <c r="C17">
-        <v>346.6481263407594</v>
+        <v>344.6102905817654</v>
       </c>
       <c r="D17">
-        <v>385.3581263407594</v>
+        <v>387.4142905817654</v>
       </c>
       <c r="E17">
-        <v>-104.89</v>
+        <v>-100.796</v>
       </c>
       <c r="F17">
-        <v>61.41</v>
+        <v>65.50399999999999</v>
       </c>
       <c r="G17">
         <v>22.7</v>
@@ -2681,28 +2681,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M17">
-        <v>3.088923</v>
+        <v>3.294851199999999</v>
       </c>
       <c r="N17">
-        <v>49.57774366666667</v>
+        <v>49.37181546666667</v>
       </c>
       <c r="O17">
-        <v>14.8733231</v>
+        <v>14.81154464</v>
       </c>
       <c r="P17">
-        <v>34.70442056666667</v>
+        <v>34.56027082666667</v>
       </c>
       <c r="Q17">
-        <v>64.70442056666667</v>
+        <v>64.56027082666668</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1078979543830564</v>
+        <v>0.1084398213497497</v>
       </c>
       <c r="T17">
-        <v>0.903600900329636</v>
+        <v>0.9114857249398423</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.05017142436593</v>
+        <v>15.98453571034306</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09672304993378975</v>
+        <v>0.09645133864198158</v>
       </c>
       <c r="C18">
-        <v>344.6102905817654</v>
+        <v>342.5945147744755</v>
       </c>
       <c r="D18">
-        <v>387.4142905817654</v>
+        <v>389.4925147744755</v>
       </c>
       <c r="E18">
-        <v>-100.796</v>
+        <v>-96.70200000000001</v>
       </c>
       <c r="F18">
-        <v>65.50399999999999</v>
+        <v>69.598</v>
       </c>
       <c r="G18">
         <v>22.7</v>
@@ -2763,28 +2763,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M18">
-        <v>3.294851199999999</v>
+        <v>3.5007794</v>
       </c>
       <c r="N18">
-        <v>49.37181546666667</v>
+        <v>49.16588726666667</v>
       </c>
       <c r="O18">
-        <v>14.81154464</v>
+        <v>14.74976618</v>
       </c>
       <c r="P18">
-        <v>34.56027082666667</v>
+        <v>34.41612108666667</v>
       </c>
       <c r="Q18">
-        <v>64.56027082666668</v>
+        <v>64.41612108666666</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1084398213497497</v>
+        <v>0.108994745351785</v>
       </c>
       <c r="T18">
-        <v>0.9114857249398423</v>
+        <v>0.9195605453237885</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.98453571034306</v>
+        <v>15.04426890385229</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09645133864198158</v>
+        <v>0.09617962735017342</v>
       </c>
       <c r="C19">
-        <v>342.5945147744755</v>
+        <v>340.6011558451883</v>
       </c>
       <c r="D19">
-        <v>389.4925147744755</v>
+        <v>391.5931558451883</v>
       </c>
       <c r="E19">
-        <v>-96.70200000000001</v>
+        <v>-92.608</v>
       </c>
       <c r="F19">
-        <v>69.598</v>
+        <v>73.69200000000001</v>
       </c>
       <c r="G19">
         <v>22.7</v>
@@ -2845,28 +2845,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M19">
-        <v>3.5007794</v>
+        <v>3.7067076</v>
       </c>
       <c r="N19">
-        <v>49.16588726666667</v>
+        <v>48.95995906666667</v>
       </c>
       <c r="O19">
-        <v>14.74976618</v>
+        <v>14.68798772</v>
       </c>
       <c r="P19">
-        <v>34.41612108666667</v>
+        <v>34.27197134666667</v>
       </c>
       <c r="Q19">
-        <v>64.41612108666666</v>
+        <v>64.27197134666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.108994745351785</v>
+        <v>0.1095632040855773</v>
       </c>
       <c r="T19">
-        <v>0.9195605453237885</v>
+        <v>0.9278323125463673</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.04426890385229</v>
+        <v>14.20847618697161</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09617962735017344</v>
+        <v>0.09590791605836525</v>
       </c>
       <c r="C20">
-        <v>340.6011558451881</v>
+        <v>338.630578461966</v>
       </c>
       <c r="D20">
-        <v>391.5931558451882</v>
+        <v>393.716578461966</v>
       </c>
       <c r="E20">
-        <v>-92.60800000000002</v>
+        <v>-88.51400000000001</v>
       </c>
       <c r="F20">
-        <v>73.69199999999999</v>
+        <v>77.786</v>
       </c>
       <c r="G20">
         <v>22.7</v>
@@ -2927,28 +2927,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M20">
-        <v>3.7067076</v>
+        <v>3.9126358</v>
       </c>
       <c r="N20">
-        <v>48.95995906666667</v>
+        <v>48.75403086666667</v>
       </c>
       <c r="O20">
-        <v>14.68798772</v>
+        <v>14.62620926</v>
       </c>
       <c r="P20">
-        <v>34.27197134666667</v>
+        <v>34.12782160666667</v>
       </c>
       <c r="Q20">
-        <v>64.27197134666667</v>
+        <v>64.12782160666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1095632040855773</v>
+        <v>0.110145698837488</v>
       </c>
       <c r="T20">
-        <v>0.9278323125463673</v>
+        <v>0.9363083209349359</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.20847618697161</v>
+        <v>13.46066165081521</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09590791605836525</v>
+        <v>0.0958462047665571</v>
       </c>
       <c r="C21">
-        <v>338.630578461966</v>
+        <v>335.0220649993869</v>
       </c>
       <c r="D21">
-        <v>393.716578461966</v>
+        <v>394.2020649993869</v>
       </c>
       <c r="E21">
-        <v>-88.51400000000001</v>
+        <v>-84.42000000000002</v>
       </c>
       <c r="F21">
-        <v>77.786</v>
+        <v>81.88</v>
       </c>
       <c r="G21">
         <v>22.7</v>
@@ -3009,45 +3009,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M21">
-        <v>3.9126358</v>
+        <v>4.241384</v>
       </c>
       <c r="N21">
-        <v>48.75403086666667</v>
+        <v>48.42528266666667</v>
       </c>
       <c r="O21">
-        <v>14.62620926</v>
+        <v>14.5275848</v>
       </c>
       <c r="P21">
-        <v>34.12782160666667</v>
+        <v>33.89769786666668</v>
       </c>
       <c r="Q21">
-        <v>64.12782160666667</v>
+        <v>63.89769786666668</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.110145698837488</v>
+        <v>0.1107427559581964</v>
       </c>
       <c r="T21">
-        <v>0.9363083209349359</v>
+        <v>0.9449962295332188</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.46066165081521</v>
+        <v>12.41733044371051</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0958462047665571</v>
+        <v>0.09558499347474894</v>
       </c>
       <c r="C22">
-        <v>335.0220649993869</v>
+        <v>332.9963595485096</v>
       </c>
       <c r="D22">
-        <v>394.2020649993869</v>
+        <v>396.2703595485096</v>
       </c>
       <c r="E22">
-        <v>-84.42000000000002</v>
+        <v>-80.32600000000001</v>
       </c>
       <c r="F22">
-        <v>81.88</v>
+        <v>85.974</v>
       </c>
       <c r="G22">
         <v>22.7</v>
@@ -3091,28 +3091,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M22">
-        <v>4.241384</v>
+        <v>4.4534532</v>
       </c>
       <c r="N22">
-        <v>48.42528266666667</v>
+        <v>48.21321346666667</v>
       </c>
       <c r="O22">
-        <v>14.5275848</v>
+        <v>14.46396404</v>
       </c>
       <c r="P22">
-        <v>33.89769786666668</v>
+        <v>33.74924942666667</v>
       </c>
       <c r="Q22">
-        <v>63.89769786666668</v>
+        <v>63.74924942666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1107427559581964</v>
+        <v>0.1113549284490493</v>
       </c>
       <c r="T22">
-        <v>0.9449962295332188</v>
+        <v>0.9539040851846228</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.41733044371051</v>
+        <v>11.82602899401001</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09558499347474891</v>
+        <v>0.09532378218294078</v>
       </c>
       <c r="C23">
-        <v>332.9963595485099</v>
+        <v>330.9924723783534</v>
       </c>
       <c r="D23">
-        <v>396.2703595485099</v>
+        <v>398.3604723783534</v>
       </c>
       <c r="E23">
-        <v>-80.32600000000002</v>
+        <v>-76.23200000000001</v>
       </c>
       <c r="F23">
-        <v>85.97399999999999</v>
+        <v>90.068</v>
       </c>
       <c r="G23">
         <v>22.7</v>
@@ -3173,28 +3173,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M23">
-        <v>4.453453199999999</v>
+        <v>4.6655224</v>
       </c>
       <c r="N23">
-        <v>48.21321346666667</v>
+        <v>48.00114426666667</v>
       </c>
       <c r="O23">
-        <v>14.46396404</v>
+        <v>14.40034328</v>
       </c>
       <c r="P23">
-        <v>33.74924942666667</v>
+        <v>33.60080098666667</v>
       </c>
       <c r="Q23">
-        <v>63.74924942666667</v>
+        <v>63.60080098666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1113549284490493</v>
+        <v>0.1119827976704369</v>
       </c>
       <c r="T23">
-        <v>0.9539040851846226</v>
+        <v>0.9630403473911907</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.82602899401001</v>
+        <v>11.28848222155501</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09532378218294078</v>
+        <v>0.0950625708911326</v>
       </c>
       <c r="C24">
-        <v>330.9924723783534</v>
+        <v>329.0107505585813</v>
       </c>
       <c r="D24">
-        <v>398.3604723783534</v>
+        <v>400.4727505585813</v>
       </c>
       <c r="E24">
-        <v>-76.23200000000001</v>
+        <v>-72.13800000000002</v>
       </c>
       <c r="F24">
-        <v>90.068</v>
+        <v>94.16199999999999</v>
       </c>
       <c r="G24">
         <v>22.7</v>
@@ -3255,28 +3255,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M24">
-        <v>4.6655224</v>
+        <v>4.8775916</v>
       </c>
       <c r="N24">
-        <v>48.00114426666667</v>
+        <v>47.78907506666667</v>
       </c>
       <c r="O24">
-        <v>14.40034328</v>
+        <v>14.33672252</v>
       </c>
       <c r="P24">
-        <v>33.60080098666667</v>
+        <v>33.45235254666667</v>
       </c>
       <c r="Q24">
-        <v>63.60080098666667</v>
+        <v>63.45235254666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1119827976704369</v>
+        <v>0.1126269751832891</v>
       </c>
       <c r="T24">
-        <v>0.9630403473911907</v>
+        <v>0.9724139151096177</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.28848222155501</v>
+        <v>10.79767864670479</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0950625708911326</v>
+        <v>0.09480135959932444</v>
       </c>
       <c r="C25">
-        <v>329.0107505585813</v>
+        <v>327.0515485593456</v>
       </c>
       <c r="D25">
-        <v>400.4727505585813</v>
+        <v>402.6075485593456</v>
       </c>
       <c r="E25">
-        <v>-72.13800000000002</v>
+        <v>-68.04400000000001</v>
       </c>
       <c r="F25">
-        <v>94.16199999999999</v>
+        <v>98.256</v>
       </c>
       <c r="G25">
         <v>22.7</v>
@@ -3337,28 +3337,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M25">
-        <v>4.8775916</v>
+        <v>5.0896608</v>
       </c>
       <c r="N25">
-        <v>47.78907506666667</v>
+        <v>47.57700586666667</v>
       </c>
       <c r="O25">
-        <v>14.33672252</v>
+        <v>14.27310176</v>
       </c>
       <c r="P25">
-        <v>33.45235254666667</v>
+        <v>33.30390410666667</v>
       </c>
       <c r="Q25">
-        <v>63.45235254666667</v>
+        <v>63.30390410666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1126269751832891</v>
+        <v>0.1132881047359532</v>
       </c>
       <c r="T25">
-        <v>0.9724139151096177</v>
+        <v>0.9820341556627402</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.79767864670479</v>
+        <v>10.34777536975876</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09480135959932444</v>
+        <v>0.09454014830751629</v>
       </c>
       <c r="C26">
-        <v>327.0515485593456</v>
+        <v>325.1152284495948</v>
       </c>
       <c r="D26">
-        <v>402.6075485593456</v>
+        <v>404.7652284495949</v>
       </c>
       <c r="E26">
-        <v>-68.04400000000003</v>
+        <v>-63.95000000000002</v>
       </c>
       <c r="F26">
-        <v>98.25599999999999</v>
+        <v>102.35</v>
       </c>
       <c r="G26">
         <v>22.7</v>
@@ -3419,28 +3419,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M26">
-        <v>5.089660799999999</v>
+        <v>5.301729999999999</v>
       </c>
       <c r="N26">
-        <v>47.57700586666667</v>
+        <v>47.36493666666667</v>
       </c>
       <c r="O26">
-        <v>14.27310176</v>
+        <v>14.209481</v>
       </c>
       <c r="P26">
-        <v>33.30390410666667</v>
+        <v>33.15545566666667</v>
       </c>
       <c r="Q26">
-        <v>63.30390410666667</v>
+        <v>63.15545566666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1132881047359532</v>
+        <v>0.1139668644100217</v>
       </c>
       <c r="T26">
-        <v>0.9820341556627402</v>
+        <v>0.991910935963946</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.34777536975876</v>
+        <v>9.933864354968412</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09454014830751629</v>
+        <v>0.09458833701570814</v>
       </c>
       <c r="C27">
-        <v>325.1152284495948</v>
+        <v>320.6214379530736</v>
       </c>
       <c r="D27">
-        <v>404.7652284495949</v>
+        <v>404.3654379530736</v>
       </c>
       <c r="E27">
-        <v>-63.95000000000002</v>
+        <v>-59.85600000000001</v>
       </c>
       <c r="F27">
-        <v>102.35</v>
+        <v>106.444</v>
       </c>
       <c r="G27">
         <v>22.7</v>
@@ -3501,45 +3501,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M27">
-        <v>5.301729999999999</v>
+        <v>5.694754</v>
       </c>
       <c r="N27">
-        <v>47.36493666666667</v>
+        <v>46.97191266666667</v>
       </c>
       <c r="O27">
-        <v>14.209481</v>
+        <v>14.0915738</v>
       </c>
       <c r="P27">
-        <v>33.15545566666667</v>
+        <v>32.88033886666667</v>
       </c>
       <c r="Q27">
-        <v>63.15545566666667</v>
+        <v>62.88033886666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1139668644100217</v>
+        <v>0.1146639689401461</v>
       </c>
       <c r="T27">
-        <v>0.991910935963946</v>
+        <v>1.002054656273292</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.933864354968412</v>
+        <v>9.248277742404092</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09458833701570814</v>
+        <v>0.09433902572389997</v>
       </c>
       <c r="C28">
-        <v>320.6214379530736</v>
+        <v>318.6043826011202</v>
       </c>
       <c r="D28">
-        <v>404.3654379530736</v>
+        <v>406.4423826011202</v>
       </c>
       <c r="E28">
-        <v>-59.85600000000001</v>
+        <v>-55.76200000000001</v>
       </c>
       <c r="F28">
-        <v>106.444</v>
+        <v>110.538</v>
       </c>
       <c r="G28">
         <v>22.7</v>
@@ -3583,28 +3583,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M28">
-        <v>5.694754</v>
+        <v>5.913783</v>
       </c>
       <c r="N28">
-        <v>46.97191266666667</v>
+        <v>46.75288366666667</v>
       </c>
       <c r="O28">
-        <v>14.0915738</v>
+        <v>14.0258651</v>
       </c>
       <c r="P28">
-        <v>32.88033886666667</v>
+        <v>32.72701856666667</v>
       </c>
       <c r="Q28">
-        <v>62.88033886666667</v>
+        <v>62.72701856666667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1146639689401461</v>
+        <v>0.1153801722245205</v>
       </c>
       <c r="T28">
-        <v>1.002054656273292</v>
+        <v>1.012476286728101</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.248277742404092</v>
+        <v>8.905748937129866</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09433902572389997</v>
+        <v>0.0940897144320918</v>
       </c>
       <c r="C29">
-        <v>318.6043826011202</v>
+        <v>316.608773048104</v>
       </c>
       <c r="D29">
-        <v>406.4423826011202</v>
+        <v>408.540773048104</v>
       </c>
       <c r="E29">
-        <v>-55.76200000000001</v>
+        <v>-51.66800000000001</v>
       </c>
       <c r="F29">
-        <v>110.538</v>
+        <v>114.632</v>
       </c>
       <c r="G29">
         <v>22.7</v>
@@ -3665,28 +3665,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M29">
-        <v>5.913783</v>
+        <v>6.132812</v>
       </c>
       <c r="N29">
-        <v>46.75288366666667</v>
+        <v>46.53385466666667</v>
       </c>
       <c r="O29">
-        <v>14.0258651</v>
+        <v>13.9601564</v>
       </c>
       <c r="P29">
-        <v>32.72701856666667</v>
+        <v>32.57369826666667</v>
       </c>
       <c r="Q29">
-        <v>62.72701856666667</v>
+        <v>62.57369826666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1153801722245205</v>
+        <v>0.116116270044572</v>
       </c>
       <c r="T29">
-        <v>1.012476286728101</v>
+        <v>1.023187406917764</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.905748937129866</v>
+        <v>8.587686475089512</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0940897144320918</v>
+        <v>0.09384040314028363</v>
       </c>
       <c r="C30">
-        <v>316.608773048104</v>
+        <v>314.6349431804716</v>
       </c>
       <c r="D30">
-        <v>408.540773048104</v>
+        <v>410.6609431804716</v>
       </c>
       <c r="E30">
-        <v>-51.66800000000001</v>
+        <v>-47.574</v>
       </c>
       <c r="F30">
-        <v>114.632</v>
+        <v>118.726</v>
       </c>
       <c r="G30">
         <v>22.7</v>
@@ -3747,28 +3747,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M30">
-        <v>6.132812</v>
+        <v>6.351841</v>
       </c>
       <c r="N30">
-        <v>46.53385466666667</v>
+        <v>46.31482566666667</v>
       </c>
       <c r="O30">
-        <v>13.9601564</v>
+        <v>13.8944477</v>
       </c>
       <c r="P30">
-        <v>32.57369826666667</v>
+        <v>32.42037796666667</v>
       </c>
       <c r="Q30">
-        <v>62.57369826666667</v>
+        <v>62.42037796666667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.116116270044572</v>
+        <v>0.116873103014484</v>
       </c>
       <c r="T30">
-        <v>1.023187406917764</v>
+        <v>1.034200248802911</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.587686475089512</v>
+        <v>8.29155935525884</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09384040314028363</v>
+        <v>0.09359109184847549</v>
       </c>
       <c r="C31">
-        <v>314.6349431804716</v>
+        <v>312.6832338517978</v>
       </c>
       <c r="D31">
-        <v>410.6609431804716</v>
+        <v>412.8032338517978</v>
       </c>
       <c r="E31">
-        <v>-47.57400000000003</v>
+        <v>-43.48000000000002</v>
       </c>
       <c r="F31">
-        <v>118.726</v>
+        <v>122.82</v>
       </c>
       <c r="G31">
         <v>22.7</v>
@@ -3829,28 +3829,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M31">
-        <v>6.351840999999999</v>
+        <v>6.570869999999999</v>
       </c>
       <c r="N31">
-        <v>46.31482566666667</v>
+        <v>46.09579666666667</v>
       </c>
       <c r="O31">
-        <v>13.8944477</v>
+        <v>13.828739</v>
       </c>
       <c r="P31">
-        <v>32.42037796666667</v>
+        <v>32.26705766666667</v>
       </c>
       <c r="Q31">
-        <v>62.42037796666667</v>
+        <v>62.26705766666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.116873103014484</v>
+        <v>0.1176515597835364</v>
       </c>
       <c r="T31">
-        <v>1.034200248802911</v>
+        <v>1.045527743313349</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.29155935525884</v>
+        <v>8.015174043416881</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09359109184847549</v>
+        <v>0.09334178055666731</v>
       </c>
       <c r="C32">
-        <v>312.6832338517978</v>
+        <v>310.7539930654648</v>
       </c>
       <c r="D32">
-        <v>412.8032338517978</v>
+        <v>414.9679930654648</v>
       </c>
       <c r="E32">
-        <v>-43.48000000000002</v>
+        <v>-39.38600000000002</v>
       </c>
       <c r="F32">
-        <v>122.82</v>
+        <v>126.914</v>
       </c>
       <c r="G32">
         <v>22.7</v>
@@ -3911,28 +3911,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M32">
-        <v>6.570869999999999</v>
+        <v>6.789898999999999</v>
       </c>
       <c r="N32">
-        <v>46.09579666666667</v>
+        <v>45.87676766666667</v>
       </c>
       <c r="O32">
-        <v>13.828739</v>
+        <v>13.7630303</v>
       </c>
       <c r="P32">
-        <v>32.26705766666667</v>
+        <v>32.11373736666667</v>
       </c>
       <c r="Q32">
-        <v>62.26705766666667</v>
+        <v>62.11373736666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1176515597835364</v>
+        <v>0.1184525805169092</v>
       </c>
       <c r="T32">
-        <v>1.045527743313349</v>
+        <v>1.057183570998001</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.015174043416881</v>
+        <v>7.756620042016336</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09334178055666731</v>
+        <v>0.09327166926485915</v>
       </c>
       <c r="C33">
-        <v>310.7539930654648</v>
+        <v>307.2728626464887</v>
       </c>
       <c r="D33">
-        <v>414.9679930654648</v>
+        <v>415.5808626464887</v>
       </c>
       <c r="E33">
-        <v>-39.38600000000002</v>
+        <v>-35.29200000000003</v>
       </c>
       <c r="F33">
-        <v>126.914</v>
+        <v>131.008</v>
       </c>
       <c r="G33">
         <v>22.7</v>
@@ -3993,45 +3993,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M33">
-        <v>6.789898999999999</v>
+        <v>7.113734399999999</v>
       </c>
       <c r="N33">
-        <v>45.87676766666667</v>
+        <v>45.55293226666667</v>
       </c>
       <c r="O33">
-        <v>13.7630303</v>
+        <v>13.66587968</v>
       </c>
       <c r="P33">
-        <v>32.11373736666667</v>
+        <v>31.88705258666667</v>
       </c>
       <c r="Q33">
-        <v>62.11373736666667</v>
+        <v>61.88705258666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1184525805169092</v>
+        <v>0.1192771606836164</v>
       </c>
       <c r="T33">
-        <v>1.057183570998001</v>
+        <v>1.069182217143967</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.756620042016336</v>
+        <v>7.403518841899225</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09327166926485915</v>
+        <v>0.093027957973051</v>
       </c>
       <c r="C34">
-        <v>307.2728626464887</v>
+        <v>305.3233921420074</v>
       </c>
       <c r="D34">
-        <v>415.5808626464887</v>
+        <v>417.7253921420074</v>
       </c>
       <c r="E34">
-        <v>-35.29200000000003</v>
+        <v>-31.19800000000001</v>
       </c>
       <c r="F34">
-        <v>131.008</v>
+        <v>135.102</v>
       </c>
       <c r="G34">
         <v>22.7</v>
@@ -4075,28 +4075,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M34">
-        <v>7.113734399999999</v>
+        <v>7.3360386</v>
       </c>
       <c r="N34">
-        <v>45.55293226666667</v>
+        <v>45.33062806666667</v>
       </c>
       <c r="O34">
-        <v>13.66587968</v>
+        <v>13.59918842</v>
       </c>
       <c r="P34">
-        <v>31.88705258666667</v>
+        <v>31.73143964666667</v>
       </c>
       <c r="Q34">
-        <v>61.88705258666667</v>
+        <v>61.73143964666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1192771606836164</v>
+        <v>0.1201263551836582</v>
       </c>
       <c r="T34">
-        <v>1.069182217143967</v>
+        <v>1.081539031831604</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.403518841899225</v>
+        <v>7.179169786084096</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.093027957973051</v>
+        <v>0.09278424668124284</v>
       </c>
       <c r="C35">
-        <v>305.3233921420074</v>
+        <v>303.3961693520513</v>
       </c>
       <c r="D35">
-        <v>417.7253921420074</v>
+        <v>419.8921693520513</v>
       </c>
       <c r="E35">
-        <v>-31.19800000000001</v>
+        <v>-27.10400000000001</v>
       </c>
       <c r="F35">
-        <v>135.102</v>
+        <v>139.196</v>
       </c>
       <c r="G35">
         <v>22.7</v>
@@ -4157,28 +4157,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M35">
-        <v>7.3360386</v>
+        <v>7.5583428</v>
       </c>
       <c r="N35">
-        <v>45.33062806666667</v>
+        <v>45.10832386666667</v>
       </c>
       <c r="O35">
-        <v>13.59918842</v>
+        <v>13.53249716</v>
       </c>
       <c r="P35">
-        <v>31.73143964666667</v>
+        <v>31.57582670666667</v>
       </c>
       <c r="Q35">
-        <v>61.73143964666667</v>
+        <v>61.57582670666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1201263551836582</v>
+        <v>0.121001282850368</v>
       </c>
       <c r="T35">
-        <v>1.081539031831604</v>
+        <v>1.094270295449169</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.179169786084096</v>
+        <v>6.968017733552211</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09278424668124284</v>
+        <v>0.09254053538943467</v>
       </c>
       <c r="C36">
-        <v>303.3961693520513</v>
+        <v>301.4915422841391</v>
       </c>
       <c r="D36">
-        <v>419.8921693520513</v>
+        <v>422.0815422841391</v>
       </c>
       <c r="E36">
-        <v>-27.10400000000001</v>
+        <v>-23.01000000000002</v>
       </c>
       <c r="F36">
-        <v>139.196</v>
+        <v>143.29</v>
       </c>
       <c r="G36">
         <v>22.7</v>
@@ -4239,28 +4239,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M36">
-        <v>7.5583428</v>
+        <v>7.780647</v>
       </c>
       <c r="N36">
-        <v>45.10832386666667</v>
+        <v>44.88601966666667</v>
       </c>
       <c r="O36">
-        <v>13.53249716</v>
+        <v>13.4658059</v>
       </c>
       <c r="P36">
-        <v>31.57582670666667</v>
+        <v>31.42021376666667</v>
       </c>
       <c r="Q36">
-        <v>61.57582670666667</v>
+        <v>61.42021376666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.121001282850368</v>
+        <v>0.1219031313683611</v>
       </c>
       <c r="T36">
-        <v>1.094270295449169</v>
+        <v>1.107393290254967</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.968017733552211</v>
+        <v>6.768931512593576</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09254053538943467</v>
+        <v>0.0922968240976265</v>
       </c>
       <c r="C37">
-        <v>301.4915422841391</v>
+        <v>299.6098662420608</v>
       </c>
       <c r="D37">
-        <v>422.0815422841391</v>
+        <v>424.2938662420608</v>
       </c>
       <c r="E37">
-        <v>-23.01000000000002</v>
+        <v>-18.916</v>
       </c>
       <c r="F37">
-        <v>143.29</v>
+        <v>147.384</v>
       </c>
       <c r="G37">
         <v>22.7</v>
@@ -4321,28 +4321,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M37">
-        <v>7.780647</v>
+        <v>8.002951200000002</v>
       </c>
       <c r="N37">
-        <v>44.88601966666667</v>
+        <v>44.66371546666667</v>
       </c>
       <c r="O37">
-        <v>13.4658059</v>
+        <v>13.39911464</v>
       </c>
       <c r="P37">
-        <v>31.42021376666667</v>
+        <v>31.26460082666667</v>
       </c>
       <c r="Q37">
-        <v>61.42021376666667</v>
+        <v>61.26460082666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1219031313683611</v>
+        <v>0.1228331626525414</v>
       </c>
       <c r="T37">
-        <v>1.107393290254967</v>
+        <v>1.120926378648446</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.768931512593576</v>
+        <v>6.580905637243753</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09229682409762652</v>
+        <v>0.09205311280581835</v>
       </c>
       <c r="C38">
-        <v>299.6098662420608</v>
+        <v>297.7515040181008</v>
       </c>
       <c r="D38">
-        <v>424.2938662420607</v>
+        <v>426.5295040181009</v>
       </c>
       <c r="E38">
-        <v>-18.91600000000003</v>
+        <v>-14.82200000000003</v>
       </c>
       <c r="F38">
-        <v>147.384</v>
+        <v>151.478</v>
       </c>
       <c r="G38">
         <v>22.7</v>
@@ -4403,28 +4403,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M38">
-        <v>8.0029512</v>
+        <v>8.225255399999998</v>
       </c>
       <c r="N38">
-        <v>44.66371546666667</v>
+        <v>44.44141126666668</v>
       </c>
       <c r="O38">
-        <v>13.39911464</v>
+        <v>13.33242338</v>
       </c>
       <c r="P38">
-        <v>31.26460082666667</v>
+        <v>31.10898788666668</v>
       </c>
       <c r="Q38">
-        <v>61.26460082666667</v>
+        <v>61.10898788666668</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1228331626525414</v>
+        <v>0.1237927187393942</v>
       </c>
       <c r="T38">
-        <v>1.120926378648446</v>
+        <v>1.134889088895686</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.580905637243755</v>
+        <v>6.403043322723655</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09205311280581835</v>
+        <v>0.09180940151401019</v>
       </c>
       <c r="C39">
-        <v>297.7515040181008</v>
+        <v>295.9168260913708</v>
       </c>
       <c r="D39">
-        <v>426.5295040181009</v>
+        <v>428.7888260913708</v>
       </c>
       <c r="E39">
-        <v>-14.82200000000003</v>
+        <v>-10.72800000000001</v>
       </c>
       <c r="F39">
-        <v>151.478</v>
+        <v>155.572</v>
       </c>
       <c r="G39">
         <v>22.7</v>
@@ -4485,28 +4485,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M39">
-        <v>8.225255399999998</v>
+        <v>8.4475596</v>
       </c>
       <c r="N39">
-        <v>44.44141126666668</v>
+        <v>44.21910706666667</v>
       </c>
       <c r="O39">
-        <v>13.33242338</v>
+        <v>13.26573212</v>
       </c>
       <c r="P39">
-        <v>31.10898788666668</v>
+        <v>30.95337494666667</v>
       </c>
       <c r="Q39">
-        <v>61.10898788666668</v>
+        <v>60.95337494666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1237927187393942</v>
+        <v>0.1247832282484035</v>
       </c>
       <c r="T39">
-        <v>1.134889088895686</v>
+        <v>1.149302209150902</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.403043322723655</v>
+        <v>6.234542182651978</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09180940151401019</v>
+        <v>0.09183869022220204</v>
       </c>
       <c r="C40">
-        <v>295.9168260913708</v>
+        <v>291.5500409460355</v>
       </c>
       <c r="D40">
-        <v>428.7888260913708</v>
+        <v>428.5160409460355</v>
       </c>
       <c r="E40">
-        <v>-10.72800000000001</v>
+        <v>-6.634000000000015</v>
       </c>
       <c r="F40">
-        <v>155.572</v>
+        <v>159.666</v>
       </c>
       <c r="G40">
         <v>22.7</v>
@@ -4567,45 +4567,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M40">
-        <v>8.4475596</v>
+        <v>8.8295298</v>
       </c>
       <c r="N40">
-        <v>44.21910706666667</v>
+        <v>43.83713686666667</v>
       </c>
       <c r="O40">
-        <v>13.26573212</v>
+        <v>13.15114106</v>
       </c>
       <c r="P40">
-        <v>30.95337494666667</v>
+        <v>30.68599580666667</v>
       </c>
       <c r="Q40">
-        <v>60.95337494666667</v>
+        <v>60.68599580666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1247832282484035</v>
+        <v>0.1258062134790197</v>
       </c>
       <c r="T40">
-        <v>1.149302209150902</v>
+        <v>1.16418789072596</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.234542182651978</v>
+        <v>5.964832540308848</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09183869022220204</v>
+        <v>0.09160197893039389</v>
       </c>
       <c r="C41">
-        <v>291.5500409460355</v>
+        <v>289.6706741994807</v>
       </c>
       <c r="D41">
-        <v>428.5160409460355</v>
+        <v>430.7306741994807</v>
       </c>
       <c r="E41">
-        <v>-6.634000000000015</v>
+        <v>-2.54000000000002</v>
       </c>
       <c r="F41">
-        <v>159.666</v>
+        <v>163.76</v>
       </c>
       <c r="G41">
         <v>22.7</v>
@@ -4649,28 +4649,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M41">
-        <v>8.8295298</v>
+        <v>9.055928</v>
       </c>
       <c r="N41">
-        <v>43.83713686666667</v>
+        <v>43.61073866666667</v>
       </c>
       <c r="O41">
-        <v>13.15114106</v>
+        <v>13.0832216</v>
       </c>
       <c r="P41">
-        <v>30.68599580666667</v>
+        <v>30.52751706666667</v>
       </c>
       <c r="Q41">
-        <v>60.68599580666667</v>
+        <v>60.52751706666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1258062134790197</v>
+        <v>0.1268632982173231</v>
       </c>
       <c r="T41">
-        <v>1.16418789072596</v>
+        <v>1.179569761686855</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.964832540308848</v>
+        <v>5.815711726801126</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09160197893039389</v>
+        <v>0.09136526763858571</v>
       </c>
       <c r="C42">
-        <v>289.6706741994807</v>
+        <v>287.8143174658361</v>
       </c>
       <c r="D42">
-        <v>430.7306741994807</v>
+        <v>432.9683174658362</v>
       </c>
       <c r="E42">
-        <v>-2.54000000000002</v>
+        <v>1.554000000000002</v>
       </c>
       <c r="F42">
-        <v>163.76</v>
+        <v>167.854</v>
       </c>
       <c r="G42">
         <v>22.7</v>
@@ -4731,28 +4731,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M42">
-        <v>9.055928</v>
+        <v>9.282326200000002</v>
       </c>
       <c r="N42">
-        <v>43.61073866666667</v>
+        <v>43.38434046666667</v>
       </c>
       <c r="O42">
-        <v>13.0832216</v>
+        <v>13.01530214</v>
       </c>
       <c r="P42">
-        <v>30.52751706666667</v>
+        <v>30.36903832666667</v>
       </c>
       <c r="Q42">
-        <v>60.52751706666667</v>
+        <v>60.36903832666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1268632982173231</v>
+        <v>0.127956216336586</v>
       </c>
       <c r="T42">
-        <v>1.179569761686855</v>
+        <v>1.195473052002355</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.815711726801126</v>
+        <v>5.673865099318172</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09136526763858571</v>
+        <v>0.09112855634677755</v>
       </c>
       <c r="C43">
-        <v>287.8143174658361</v>
+        <v>285.9813312284469</v>
       </c>
       <c r="D43">
-        <v>432.9683174658362</v>
+        <v>435.2293312284469</v>
       </c>
       <c r="E43">
-        <v>1.554000000000002</v>
+        <v>5.647999999999996</v>
       </c>
       <c r="F43">
-        <v>167.854</v>
+        <v>171.948</v>
       </c>
       <c r="G43">
         <v>22.7</v>
@@ -4813,28 +4813,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M43">
-        <v>9.282326200000002</v>
+        <v>9.5087244</v>
       </c>
       <c r="N43">
-        <v>43.38434046666667</v>
+        <v>43.15794226666667</v>
       </c>
       <c r="O43">
-        <v>13.01530214</v>
+        <v>12.94738268</v>
       </c>
       <c r="P43">
-        <v>30.36903832666667</v>
+        <v>30.21055958666667</v>
       </c>
       <c r="Q43">
-        <v>60.36903832666667</v>
+        <v>60.21055958666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.127956216336586</v>
+        <v>0.1290868212875475</v>
       </c>
       <c r="T43">
-        <v>1.195473052002355</v>
+        <v>1.21192473163908</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.673865099318172</v>
+        <v>5.53877307314393</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09112855634677756</v>
+        <v>0.0908918450549694</v>
       </c>
       <c r="C44">
-        <v>285.9813312284469</v>
+        <v>284.1720835401409</v>
       </c>
       <c r="D44">
-        <v>435.2293312284469</v>
+        <v>437.5140835401409</v>
       </c>
       <c r="E44">
-        <v>5.647999999999968</v>
+        <v>9.74199999999999</v>
       </c>
       <c r="F44">
-        <v>171.948</v>
+        <v>176.042</v>
       </c>
       <c r="G44">
         <v>22.7</v>
@@ -4895,28 +4895,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M44">
-        <v>9.508724399999998</v>
+        <v>9.7351226</v>
       </c>
       <c r="N44">
-        <v>43.15794226666667</v>
+        <v>42.93154406666667</v>
       </c>
       <c r="O44">
-        <v>12.94738268</v>
+        <v>12.87946322</v>
       </c>
       <c r="P44">
-        <v>30.21055958666667</v>
+        <v>30.05208084666667</v>
       </c>
       <c r="Q44">
-        <v>60.21055958666667</v>
+        <v>60.05208084666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1290868212875475</v>
+        <v>0.1302570965876656</v>
       </c>
       <c r="T44">
-        <v>1.21192473163908</v>
+        <v>1.228953663192883</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.538773073143931</v>
+        <v>5.409964397024304</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0908918450549694</v>
+        <v>0.09065513376316124</v>
       </c>
       <c r="C45">
-        <v>284.1720835401409</v>
+        <v>282.3869502229576</v>
       </c>
       <c r="D45">
-        <v>437.5140835401409</v>
+        <v>439.8229502229576</v>
       </c>
       <c r="E45">
-        <v>9.74199999999999</v>
+        <v>13.83599999999998</v>
       </c>
       <c r="F45">
-        <v>176.042</v>
+        <v>180.136</v>
       </c>
       <c r="G45">
         <v>22.7</v>
@@ -4977,28 +4977,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M45">
-        <v>9.7351226</v>
+        <v>9.961520800000001</v>
       </c>
       <c r="N45">
-        <v>42.93154406666667</v>
+        <v>42.70514586666667</v>
       </c>
       <c r="O45">
-        <v>12.87946322</v>
+        <v>12.81154376</v>
       </c>
       <c r="P45">
-        <v>30.05208084666667</v>
+        <v>29.89360210666667</v>
       </c>
       <c r="Q45">
-        <v>60.05208084666667</v>
+        <v>59.89360210666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1302570965876656</v>
+        <v>0.1314691674342165</v>
       </c>
       <c r="T45">
-        <v>1.228953663192883</v>
+        <v>1.246590770873608</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.409964397024304</v>
+        <v>5.287010660728297</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09065513376316124</v>
+        <v>0.09041842247135308</v>
       </c>
       <c r="C46">
-        <v>282.3869502229576</v>
+        <v>280.6263150742361</v>
       </c>
       <c r="D46">
-        <v>439.8229502229576</v>
+        <v>442.1563150742361</v>
       </c>
       <c r="E46">
-        <v>13.83599999999998</v>
+        <v>17.92999999999998</v>
       </c>
       <c r="F46">
-        <v>180.136</v>
+        <v>184.23</v>
       </c>
       <c r="G46">
         <v>22.7</v>
@@ -5059,28 +5059,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M46">
-        <v>9.961520800000001</v>
+        <v>10.187919</v>
       </c>
       <c r="N46">
-        <v>42.70514586666667</v>
+        <v>42.47874766666667</v>
       </c>
       <c r="O46">
-        <v>12.81154376</v>
+        <v>12.7436243</v>
       </c>
       <c r="P46">
-        <v>29.89360210666667</v>
+        <v>29.73512336666667</v>
       </c>
       <c r="Q46">
-        <v>59.89360210666667</v>
+        <v>59.73512336666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1314691674342165</v>
+        <v>0.1327253135842783</v>
       </c>
       <c r="T46">
-        <v>1.246590770873608</v>
+        <v>1.26486922792454</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.287010660728297</v>
+        <v>5.169521534934335</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09041842247135308</v>
+        <v>0.0901817111795449</v>
       </c>
       <c r="C47">
-        <v>280.6263150742361</v>
+        <v>278.8905700792978</v>
       </c>
       <c r="D47">
-        <v>442.1563150742361</v>
+        <v>444.5145700792978</v>
       </c>
       <c r="E47">
-        <v>17.92999999999998</v>
+        <v>22.02399999999997</v>
       </c>
       <c r="F47">
-        <v>184.23</v>
+        <v>188.324</v>
       </c>
       <c r="G47">
         <v>22.7</v>
@@ -5141,28 +5141,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M47">
-        <v>10.187919</v>
+        <v>10.4143172</v>
       </c>
       <c r="N47">
-        <v>42.47874766666667</v>
+        <v>42.25234946666667</v>
       </c>
       <c r="O47">
-        <v>12.7436243</v>
+        <v>12.67570484</v>
       </c>
       <c r="P47">
-        <v>29.73512336666667</v>
+        <v>29.57664462666667</v>
       </c>
       <c r="Q47">
-        <v>59.73512336666667</v>
+        <v>59.57664462666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1327253135842783</v>
+        <v>0.1340279836658239</v>
       </c>
       <c r="T47">
-        <v>1.26486922792454</v>
+        <v>1.283824664866248</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.169521534934335</v>
+        <v>5.05714063200098</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0901817111795449</v>
+        <v>0.08994499988773674</v>
       </c>
       <c r="C48">
-        <v>278.8905700792978</v>
+        <v>277.1801156309708</v>
       </c>
       <c r="D48">
-        <v>444.5145700792978</v>
+        <v>446.8981156309708</v>
       </c>
       <c r="E48">
-        <v>22.02399999999997</v>
+        <v>26.11799999999999</v>
       </c>
       <c r="F48">
-        <v>188.324</v>
+        <v>192.418</v>
       </c>
       <c r="G48">
         <v>22.7</v>
@@ -5223,28 +5223,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M48">
-        <v>10.4143172</v>
+        <v>10.6407154</v>
       </c>
       <c r="N48">
-        <v>42.25234946666667</v>
+        <v>42.02595126666667</v>
       </c>
       <c r="O48">
-        <v>12.67570484</v>
+        <v>12.60778538</v>
       </c>
       <c r="P48">
-        <v>29.57664462666667</v>
+        <v>29.41816588666667</v>
       </c>
       <c r="Q48">
-        <v>59.57664462666667</v>
+        <v>59.41816588666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1340279836658239</v>
+        <v>0.1353798111089373</v>
       </c>
       <c r="T48">
-        <v>1.283824664866248</v>
+        <v>1.30349540131519</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.05714063200098</v>
+        <v>4.949541895149894</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08994499988773674</v>
+        <v>0.08970828859592858</v>
       </c>
       <c r="C49">
-        <v>277.1801156309708</v>
+        <v>275.495360756217</v>
       </c>
       <c r="D49">
-        <v>446.8981156309708</v>
+        <v>449.307360756217</v>
       </c>
       <c r="E49">
-        <v>26.11799999999999</v>
+        <v>30.21199999999999</v>
       </c>
       <c r="F49">
-        <v>192.418</v>
+        <v>196.512</v>
       </c>
       <c r="G49">
         <v>22.7</v>
@@ -5305,28 +5305,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M49">
-        <v>10.6407154</v>
+        <v>10.8671136</v>
       </c>
       <c r="N49">
-        <v>42.02595126666667</v>
+        <v>41.79955306666668</v>
       </c>
       <c r="O49">
-        <v>12.60778538</v>
+        <v>12.53986592</v>
       </c>
       <c r="P49">
-        <v>29.41816588666667</v>
+        <v>29.25968714666667</v>
       </c>
       <c r="Q49">
-        <v>59.41816588666667</v>
+        <v>59.25968714666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1353798111089373</v>
+        <v>0.1367836319152473</v>
       </c>
       <c r="T49">
-        <v>1.30349540131519</v>
+        <v>1.323922704550631</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.949541895149894</v>
+        <v>4.84642643900094</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08970828859592858</v>
+        <v>0.08947157730412043</v>
       </c>
       <c r="C50">
-        <v>275.495360756217</v>
+        <v>273.8367233501272</v>
       </c>
       <c r="D50">
-        <v>449.307360756217</v>
+        <v>451.7427233501272</v>
       </c>
       <c r="E50">
-        <v>30.21199999999996</v>
+        <v>34.30599999999998</v>
       </c>
       <c r="F50">
-        <v>196.512</v>
+        <v>200.606</v>
       </c>
       <c r="G50">
         <v>22.7</v>
@@ -5387,28 +5387,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M50">
-        <v>10.8671136</v>
+        <v>11.0935118</v>
       </c>
       <c r="N50">
-        <v>41.79955306666668</v>
+        <v>41.57315486666667</v>
       </c>
       <c r="O50">
-        <v>12.53986592</v>
+        <v>12.47194646</v>
       </c>
       <c r="P50">
-        <v>29.25968714666667</v>
+        <v>29.10120840666667</v>
       </c>
       <c r="Q50">
-        <v>59.25968714666667</v>
+        <v>59.10120840666667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1367836319152473</v>
+        <v>0.1382425045178832</v>
       </c>
       <c r="T50">
-        <v>1.323922704550631</v>
+        <v>1.345151078501186</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.84642643900094</v>
+        <v>4.747519776980511</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08947157730412043</v>
+        <v>0.08923486601231227</v>
       </c>
       <c r="C51">
-        <v>273.8367233501272</v>
+        <v>272.20463041757</v>
       </c>
       <c r="D51">
-        <v>451.7427233501272</v>
+        <v>454.20463041757</v>
       </c>
       <c r="E51">
-        <v>34.30599999999998</v>
+        <v>38.39999999999998</v>
       </c>
       <c r="F51">
-        <v>200.606</v>
+        <v>204.7</v>
       </c>
       <c r="G51">
         <v>22.7</v>
@@ -5469,28 +5469,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M51">
-        <v>11.0935118</v>
+        <v>11.31991</v>
       </c>
       <c r="N51">
-        <v>41.57315486666667</v>
+        <v>41.34675666666667</v>
       </c>
       <c r="O51">
-        <v>12.47194646</v>
+        <v>12.404027</v>
       </c>
       <c r="P51">
-        <v>29.10120840666667</v>
+        <v>28.94272966666667</v>
       </c>
       <c r="Q51">
-        <v>59.10120840666667</v>
+        <v>58.94272966666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1382425045178832</v>
+        <v>0.1397597320246246</v>
       </c>
       <c r="T51">
-        <v>1.345151078501186</v>
+        <v>1.367228587409763</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.747519776980511</v>
+        <v>4.652569381440902</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08923486601231227</v>
+        <v>0.0889981547205041</v>
       </c>
       <c r="C52">
-        <v>272.20463041757</v>
+        <v>270.5995183227834</v>
       </c>
       <c r="D52">
-        <v>454.20463041757</v>
+        <v>456.6935183227834</v>
       </c>
       <c r="E52">
-        <v>38.39999999999998</v>
+        <v>42.49399999999997</v>
       </c>
       <c r="F52">
-        <v>204.7</v>
+        <v>208.794</v>
       </c>
       <c r="G52">
         <v>22.7</v>
@@ -5551,28 +5551,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M52">
-        <v>11.31991</v>
+        <v>11.5463082</v>
       </c>
       <c r="N52">
-        <v>41.34675666666667</v>
+        <v>41.12035846666667</v>
       </c>
       <c r="O52">
-        <v>12.404027</v>
+        <v>12.33610754</v>
       </c>
       <c r="P52">
-        <v>28.94272966666667</v>
+        <v>28.78425092666667</v>
       </c>
       <c r="Q52">
-        <v>58.94272966666667</v>
+        <v>58.78425092666667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1397597320246246</v>
+        <v>0.1413388871847022</v>
       </c>
       <c r="T52">
-        <v>1.367228587409763</v>
+        <v>1.390207219130936</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.652569381440902</v>
+        <v>4.561342530824414</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0889981547205041</v>
+        <v>0.08967144342869593</v>
       </c>
       <c r="C53">
-        <v>270.5995183227834</v>
+        <v>259.4967088339666</v>
       </c>
       <c r="D53">
-        <v>456.6935183227834</v>
+        <v>449.6847088339667</v>
       </c>
       <c r="E53">
-        <v>42.49399999999997</v>
+        <v>46.58799999999999</v>
       </c>
       <c r="F53">
-        <v>208.794</v>
+        <v>212.888</v>
       </c>
       <c r="G53">
         <v>22.7</v>
@@ -5633,45 +5633,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M53">
-        <v>11.5463082</v>
+        <v>12.3049264</v>
       </c>
       <c r="N53">
-        <v>41.12035846666667</v>
+        <v>40.36174026666667</v>
       </c>
       <c r="O53">
-        <v>12.33610754</v>
+        <v>12.10852208</v>
       </c>
       <c r="P53">
-        <v>28.78425092666667</v>
+        <v>28.25321818666667</v>
       </c>
       <c r="Q53">
-        <v>58.78425092666667</v>
+        <v>58.25321818666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1413388871847022</v>
+        <v>0.1429838404764499</v>
       </c>
       <c r="T53">
-        <v>1.390207219130936</v>
+        <v>1.414143293840491</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.561342530824414</v>
+        <v>4.28012853995345</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08967144342869593</v>
+        <v>0.08945223213688779</v>
       </c>
       <c r="C54">
-        <v>259.4967088339666</v>
+        <v>257.6609201808857</v>
       </c>
       <c r="D54">
-        <v>449.6847088339667</v>
+        <v>451.9429201808857</v>
       </c>
       <c r="E54">
-        <v>46.58799999999999</v>
+        <v>50.68199999999999</v>
       </c>
       <c r="F54">
-        <v>212.888</v>
+        <v>216.982</v>
       </c>
       <c r="G54">
         <v>22.7</v>
@@ -5715,28 +5715,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M54">
-        <v>12.3049264</v>
+        <v>12.5415596</v>
       </c>
       <c r="N54">
-        <v>40.36174026666667</v>
+        <v>40.12510706666667</v>
       </c>
       <c r="O54">
-        <v>12.10852208</v>
+        <v>12.03753212</v>
       </c>
       <c r="P54">
-        <v>28.25321818666667</v>
+        <v>28.08757494666667</v>
       </c>
       <c r="Q54">
-        <v>58.25321818666667</v>
+        <v>58.08757494666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1429838404764499</v>
+        <v>0.1446987917806123</v>
       </c>
       <c r="T54">
-        <v>1.414143293840491</v>
+        <v>1.439097924920665</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.28012853995345</v>
+        <v>4.199371397690178</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08945223213688779</v>
+        <v>0.08923302084507963</v>
       </c>
       <c r="C55">
-        <v>257.6609201808857</v>
+        <v>255.8479264159753</v>
       </c>
       <c r="D55">
-        <v>451.9429201808857</v>
+        <v>454.2239264159753</v>
       </c>
       <c r="E55">
-        <v>50.68199999999999</v>
+        <v>54.77599999999998</v>
       </c>
       <c r="F55">
-        <v>216.982</v>
+        <v>221.076</v>
       </c>
       <c r="G55">
         <v>22.7</v>
@@ -5797,28 +5797,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M55">
-        <v>12.5415596</v>
+        <v>12.7781928</v>
       </c>
       <c r="N55">
-        <v>40.12510706666667</v>
+        <v>39.88847386666667</v>
       </c>
       <c r="O55">
-        <v>12.03753212</v>
+        <v>11.96654216</v>
       </c>
       <c r="P55">
-        <v>28.08757494666667</v>
+        <v>27.92193170666667</v>
       </c>
       <c r="Q55">
-        <v>58.08757494666667</v>
+        <v>57.92193170666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1446987917806123</v>
+        <v>0.1464883061849557</v>
       </c>
       <c r="T55">
-        <v>1.439097924920665</v>
+        <v>1.465137539960846</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.199371397690178</v>
+        <v>4.121605260695915</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08923302084507963</v>
+        <v>0.08901380955327146</v>
       </c>
       <c r="C56">
-        <v>255.8479264159753</v>
+        <v>254.0580744350727</v>
       </c>
       <c r="D56">
-        <v>454.2239264159753</v>
+        <v>456.5280744350728</v>
       </c>
       <c r="E56">
-        <v>54.77599999999998</v>
+        <v>58.87</v>
       </c>
       <c r="F56">
-        <v>221.076</v>
+        <v>225.17</v>
       </c>
       <c r="G56">
         <v>22.7</v>
@@ -5879,28 +5879,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M56">
-        <v>12.7781928</v>
+        <v>13.014826</v>
       </c>
       <c r="N56">
-        <v>39.88847386666667</v>
+        <v>39.65184066666667</v>
       </c>
       <c r="O56">
-        <v>11.96654216</v>
+        <v>11.8955522</v>
       </c>
       <c r="P56">
-        <v>27.92193170666667</v>
+        <v>27.75628846666667</v>
       </c>
       <c r="Q56">
-        <v>57.92193170666667</v>
+        <v>57.75628846666667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1464883061849557</v>
+        <v>0.1483573545628255</v>
       </c>
       <c r="T56">
-        <v>1.465137539960846</v>
+        <v>1.492334471225036</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.121605260695915</v>
+        <v>4.046666983228716</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08901380955327146</v>
+        <v>0.0901665982614633</v>
       </c>
       <c r="C57">
-        <v>254.0580744350727</v>
+        <v>238.1019883206536</v>
       </c>
       <c r="D57">
-        <v>456.5280744350728</v>
+        <v>444.6659883206536</v>
       </c>
       <c r="E57">
-        <v>58.87</v>
+        <v>62.964</v>
       </c>
       <c r="F57">
-        <v>225.17</v>
+        <v>229.264</v>
       </c>
       <c r="G57">
         <v>22.7</v>
@@ -5961,45 +5961,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M57">
-        <v>13.014826</v>
+        <v>14.0538832</v>
       </c>
       <c r="N57">
-        <v>39.65184066666667</v>
+        <v>38.61278346666667</v>
       </c>
       <c r="O57">
-        <v>11.8955522</v>
+        <v>11.58383504</v>
       </c>
       <c r="P57">
-        <v>27.75628846666667</v>
+        <v>27.02894842666667</v>
       </c>
       <c r="Q57">
-        <v>57.75628846666667</v>
+        <v>57.02894842666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1483573545628255</v>
+        <v>0.1503113596851439</v>
       </c>
       <c r="T57">
-        <v>1.492334471225036</v>
+        <v>1.520767626637598</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.046666983228716</v>
+        <v>3.747481455279682</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0901665982614633</v>
+        <v>0.08997188696965513</v>
       </c>
       <c r="C58">
-        <v>238.1019883206536</v>
+        <v>235.9680922453183</v>
       </c>
       <c r="D58">
-        <v>444.6659883206536</v>
+        <v>446.6260922453183</v>
       </c>
       <c r="E58">
-        <v>62.964</v>
+        <v>67.05799999999999</v>
       </c>
       <c r="F58">
-        <v>229.264</v>
+        <v>233.358</v>
       </c>
       <c r="G58">
         <v>22.7</v>
@@ -6043,28 +6043,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M58">
-        <v>14.0538832</v>
+        <v>14.3048454</v>
       </c>
       <c r="N58">
-        <v>38.61278346666667</v>
+        <v>38.36182126666667</v>
       </c>
       <c r="O58">
-        <v>11.58383504</v>
+        <v>11.50854638</v>
       </c>
       <c r="P58">
-        <v>27.02894842666667</v>
+        <v>26.85327488666667</v>
       </c>
       <c r="Q58">
-        <v>57.02894842666667</v>
+        <v>56.85327488666667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1503113596851439</v>
+        <v>0.1523562487666399</v>
       </c>
       <c r="T58">
-        <v>1.520767626637598</v>
+        <v>1.55052325439493</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.747481455279682</v>
+        <v>3.681736166590565</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08997188696965513</v>
+        <v>0.08977717567784697</v>
       </c>
       <c r="C59">
-        <v>235.9680922453183</v>
+        <v>233.8515530994068</v>
       </c>
       <c r="D59">
-        <v>446.6260922453183</v>
+        <v>448.6035530994068</v>
       </c>
       <c r="E59">
-        <v>67.05799999999999</v>
+        <v>71.15200000000002</v>
       </c>
       <c r="F59">
-        <v>233.358</v>
+        <v>237.452</v>
       </c>
       <c r="G59">
         <v>22.7</v>
@@ -6125,28 +6125,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M59">
-        <v>14.3048454</v>
+        <v>14.5558076</v>
       </c>
       <c r="N59">
-        <v>38.36182126666667</v>
+        <v>38.11085906666667</v>
       </c>
       <c r="O59">
-        <v>11.50854638</v>
+        <v>11.43325772</v>
       </c>
       <c r="P59">
-        <v>26.85327488666667</v>
+        <v>26.67760134666667</v>
       </c>
       <c r="Q59">
-        <v>56.85327488666667</v>
+        <v>56.67760134666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1523562487666399</v>
+        <v>0.1544985135186833</v>
       </c>
       <c r="T59">
-        <v>1.55052325439493</v>
+        <v>1.581695816807373</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.681736166590565</v>
+        <v>3.618257956821761</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08977717567784697</v>
+        <v>0.08958246438603881</v>
       </c>
       <c r="C60">
-        <v>233.8515530994069</v>
+        <v>231.7526024544078</v>
       </c>
       <c r="D60">
-        <v>448.6035530994068</v>
+        <v>450.5986024544078</v>
       </c>
       <c r="E60">
-        <v>71.15199999999996</v>
+        <v>75.24599999999995</v>
       </c>
       <c r="F60">
-        <v>237.452</v>
+        <v>241.546</v>
       </c>
       <c r="G60">
         <v>22.7</v>
@@ -6207,28 +6207,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M60">
-        <v>14.5558076</v>
+        <v>14.8067698</v>
       </c>
       <c r="N60">
-        <v>38.11085906666668</v>
+        <v>37.85989686666667</v>
       </c>
       <c r="O60">
-        <v>11.43325772</v>
+        <v>11.35796906</v>
       </c>
       <c r="P60">
-        <v>26.67760134666668</v>
+        <v>26.50192780666667</v>
       </c>
       <c r="Q60">
-        <v>56.67760134666668</v>
+        <v>56.50192780666667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1544985135186833</v>
+        <v>0.1567452789903385</v>
       </c>
       <c r="T60">
-        <v>1.581695816807373</v>
+        <v>1.614388992020423</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.618257956821763</v>
+        <v>3.556931550773936</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08958246438603881</v>
+        <v>0.09056375309423066</v>
       </c>
       <c r="C61">
-        <v>231.7526024544078</v>
+        <v>217.78080423707</v>
       </c>
       <c r="D61">
-        <v>450.5986024544078</v>
+        <v>440.72080423707</v>
       </c>
       <c r="E61">
-        <v>75.24599999999995</v>
+        <v>79.33999999999997</v>
       </c>
       <c r="F61">
-        <v>241.546</v>
+        <v>245.64</v>
       </c>
       <c r="G61">
         <v>22.7</v>
@@ -6289,45 +6289,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M61">
-        <v>14.8067698</v>
+        <v>15.745524</v>
       </c>
       <c r="N61">
-        <v>37.85989686666667</v>
+        <v>36.92114266666667</v>
       </c>
       <c r="O61">
-        <v>11.35796906</v>
+        <v>11.0763428</v>
       </c>
       <c r="P61">
-        <v>26.50192780666667</v>
+        <v>25.84479986666667</v>
       </c>
       <c r="Q61">
-        <v>56.50192780666667</v>
+        <v>55.84479986666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1567452789903385</v>
+        <v>0.1591043827355766</v>
       </c>
       <c r="T61">
-        <v>1.614388992020423</v>
+        <v>1.648716825994126</v>
       </c>
       <c r="U61">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.556931550773936</v>
+        <v>3.344865922954782</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09056375309423066</v>
+        <v>0.0903886418024225</v>
       </c>
       <c r="C62">
-        <v>217.78080423707</v>
+        <v>215.4176304348865</v>
       </c>
       <c r="D62">
-        <v>440.72080423707</v>
+        <v>442.4516304348865</v>
       </c>
       <c r="E62">
-        <v>79.33999999999997</v>
+        <v>83.43399999999997</v>
       </c>
       <c r="F62">
-        <v>245.64</v>
+        <v>249.734</v>
       </c>
       <c r="G62">
         <v>22.7</v>
@@ -6371,28 +6371,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M62">
-        <v>15.745524</v>
+        <v>16.0079494</v>
       </c>
       <c r="N62">
-        <v>36.92114266666667</v>
+        <v>36.65871726666667</v>
       </c>
       <c r="O62">
-        <v>11.0763428</v>
+        <v>10.99761518</v>
       </c>
       <c r="P62">
-        <v>25.84479986666667</v>
+        <v>25.66110208666667</v>
       </c>
       <c r="Q62">
-        <v>55.84479986666667</v>
+        <v>55.66110208666667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1591043827355766</v>
+        <v>0.1615844661600577</v>
       </c>
       <c r="T62">
-        <v>1.648716825994126</v>
+        <v>1.68480506171007</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.344865922954782</v>
+        <v>3.290032055365359</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0903886418024225</v>
+        <v>0.09021353051061433</v>
       </c>
       <c r="C63">
-        <v>215.4176304348865</v>
+        <v>213.0681050505572</v>
       </c>
       <c r="D63">
-        <v>442.4516304348865</v>
+        <v>444.1961050505572</v>
       </c>
       <c r="E63">
-        <v>83.43399999999997</v>
+        <v>87.52799999999996</v>
       </c>
       <c r="F63">
-        <v>249.734</v>
+        <v>253.828</v>
       </c>
       <c r="G63">
         <v>22.7</v>
@@ -6453,28 +6453,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M63">
-        <v>16.0079494</v>
+        <v>16.2703748</v>
       </c>
       <c r="N63">
-        <v>36.65871726666667</v>
+        <v>36.39629186666667</v>
       </c>
       <c r="O63">
-        <v>10.99761518</v>
+        <v>10.91888756</v>
       </c>
       <c r="P63">
-        <v>25.66110208666667</v>
+        <v>25.47740430666667</v>
       </c>
       <c r="Q63">
-        <v>55.66110208666667</v>
+        <v>55.47740430666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1615844661600577</v>
+        <v>0.1641950802910903</v>
       </c>
       <c r="T63">
-        <v>1.68480506171007</v>
+        <v>1.722792678253169</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.290032055365359</v>
+        <v>3.236967022214305</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09021353051061433</v>
+        <v>0.09003841921880618</v>
       </c>
       <c r="C64">
-        <v>213.0681050505572</v>
+        <v>210.7323901598608</v>
       </c>
       <c r="D64">
-        <v>444.1961050505572</v>
+        <v>445.9543901598607</v>
       </c>
       <c r="E64">
-        <v>87.52799999999996</v>
+        <v>91.62199999999996</v>
       </c>
       <c r="F64">
-        <v>253.828</v>
+        <v>257.922</v>
       </c>
       <c r="G64">
         <v>22.7</v>
@@ -6535,28 +6535,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M64">
-        <v>16.2703748</v>
+        <v>16.5328002</v>
       </c>
       <c r="N64">
-        <v>36.39629186666667</v>
+        <v>36.13386646666667</v>
       </c>
       <c r="O64">
-        <v>10.91888756</v>
+        <v>10.84015994</v>
       </c>
       <c r="P64">
-        <v>25.47740430666667</v>
+        <v>25.29370652666667</v>
       </c>
       <c r="Q64">
-        <v>55.47740430666667</v>
+        <v>55.29370652666667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1641950802910903</v>
+        <v>0.1669468086994761</v>
       </c>
       <c r="T64">
-        <v>1.722792678253169</v>
+        <v>1.762833679474274</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.236967022214305</v>
+        <v>3.185586593290269</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09003841921880618</v>
+        <v>0.08986330792699801</v>
       </c>
       <c r="C65">
-        <v>210.7323901598608</v>
+        <v>208.4106504149872</v>
       </c>
       <c r="D65">
-        <v>445.9543901598607</v>
+        <v>447.7266504149871</v>
       </c>
       <c r="E65">
-        <v>91.62199999999996</v>
+        <v>95.71599999999995</v>
       </c>
       <c r="F65">
-        <v>257.922</v>
+        <v>262.016</v>
       </c>
       <c r="G65">
         <v>22.7</v>
@@ -6617,28 +6617,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M65">
-        <v>16.5328002</v>
+        <v>16.7952256</v>
       </c>
       <c r="N65">
-        <v>36.13386646666667</v>
+        <v>35.87144106666668</v>
       </c>
       <c r="O65">
-        <v>10.84015994</v>
+        <v>10.76143232</v>
       </c>
       <c r="P65">
-        <v>25.29370652666667</v>
+        <v>25.11000874666667</v>
       </c>
       <c r="Q65">
-        <v>55.29370652666667</v>
+        <v>55.11000874666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1669468086994761</v>
+        <v>0.1698514109083278</v>
       </c>
       <c r="T65">
-        <v>1.762833679474274</v>
+        <v>1.805099180763217</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.185586593290269</v>
+        <v>3.135811802770109</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08986330792699801</v>
+        <v>0.08968819663518984</v>
       </c>
       <c r="C66">
-        <v>208.4106504149872</v>
+        <v>206.1030530959359</v>
       </c>
       <c r="D66">
-        <v>447.7266504149871</v>
+        <v>449.513053095936</v>
       </c>
       <c r="E66">
-        <v>95.71599999999995</v>
+        <v>99.81</v>
       </c>
       <c r="F66">
-        <v>262.016</v>
+        <v>266.11</v>
       </c>
       <c r="G66">
         <v>22.7</v>
@@ -6699,28 +6699,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M66">
-        <v>16.7952256</v>
+        <v>17.057651</v>
       </c>
       <c r="N66">
-        <v>35.87144106666668</v>
+        <v>35.60901566666666</v>
       </c>
       <c r="O66">
-        <v>10.76143232</v>
+        <v>10.6827047</v>
       </c>
       <c r="P66">
-        <v>25.11000874666667</v>
+        <v>24.92631096666667</v>
       </c>
       <c r="Q66">
-        <v>55.11000874666667</v>
+        <v>54.92631096666666</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1698514109083278</v>
+        <v>0.1729219903862567</v>
       </c>
       <c r="T66">
-        <v>1.805099180763217</v>
+        <v>1.849779853554386</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.135811802770109</v>
+        <v>3.087568544265952</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08968819663518984</v>
+        <v>0.08951308534338169</v>
       </c>
       <c r="C67">
-        <v>206.1030530959359</v>
+        <v>203.8097681631504</v>
       </c>
       <c r="D67">
-        <v>449.513053095936</v>
+        <v>451.3137681631504</v>
       </c>
       <c r="E67">
-        <v>99.81</v>
+        <v>103.904</v>
       </c>
       <c r="F67">
-        <v>266.11</v>
+        <v>270.204</v>
       </c>
       <c r="G67">
         <v>22.7</v>
@@ -6781,28 +6781,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M67">
-        <v>17.057651</v>
+        <v>17.3200764</v>
       </c>
       <c r="N67">
-        <v>35.60901566666666</v>
+        <v>35.34659026666667</v>
       </c>
       <c r="O67">
-        <v>10.6827047</v>
+        <v>10.60397708</v>
       </c>
       <c r="P67">
-        <v>24.92631096666667</v>
+        <v>24.74261318666667</v>
       </c>
       <c r="Q67">
-        <v>54.92631096666666</v>
+        <v>54.74261318666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1729219903862567</v>
+        <v>0.1761731921864167</v>
       </c>
       <c r="T67">
-        <v>1.849779853554386</v>
+        <v>1.897088801215623</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.087568544265952</v>
+        <v>3.040787202686165</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08951308534338169</v>
+        <v>0.09299617405157354</v>
       </c>
       <c r="C68">
-        <v>203.8097681631504</v>
+        <v>166.4087062809135</v>
       </c>
       <c r="D68">
-        <v>451.3137681631504</v>
+        <v>418.0067062809135</v>
       </c>
       <c r="E68">
-        <v>103.904</v>
+        <v>107.998</v>
       </c>
       <c r="F68">
-        <v>270.204</v>
+        <v>274.298</v>
       </c>
       <c r="G68">
         <v>22.7</v>
@@ -6863,45 +6863,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M68">
-        <v>17.3200764</v>
+        <v>19.7220262</v>
       </c>
       <c r="N68">
-        <v>35.34659026666667</v>
+        <v>32.94464046666667</v>
       </c>
       <c r="O68">
-        <v>10.60397708</v>
+        <v>9.88339214</v>
       </c>
       <c r="P68">
-        <v>24.74261318666667</v>
+        <v>23.06124832666667</v>
       </c>
       <c r="Q68">
-        <v>54.74261318666667</v>
+        <v>53.06124832666667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1761731921864167</v>
+        <v>0.1796214365199198</v>
       </c>
       <c r="T68">
-        <v>1.897088801215623</v>
+        <v>1.947264957826027</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.3</v>
       </c>
       <c r="W68">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.040787202686165</v>
+        <v>2.670449077218378</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09299617405157354</v>
+        <v>0.09287566275976537</v>
       </c>
       <c r="C69">
-        <v>166.4087062809135</v>
+        <v>163.3847820951502</v>
       </c>
       <c r="D69">
-        <v>418.0067062809135</v>
+        <v>419.0767820951502</v>
       </c>
       <c r="E69">
-        <v>107.998</v>
+        <v>112.092</v>
       </c>
       <c r="F69">
-        <v>274.298</v>
+        <v>278.392</v>
       </c>
       <c r="G69">
         <v>22.7</v>
@@ -6945,28 +6945,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M69">
-        <v>19.7220262</v>
+        <v>20.0163848</v>
       </c>
       <c r="N69">
-        <v>32.94464046666667</v>
+        <v>32.65028186666667</v>
       </c>
       <c r="O69">
-        <v>9.88339214</v>
+        <v>9.795084560000001</v>
       </c>
       <c r="P69">
-        <v>23.06124832666667</v>
+        <v>22.85519730666667</v>
       </c>
       <c r="Q69">
-        <v>53.06124832666667</v>
+        <v>52.85519730666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1796214365199198</v>
+        <v>0.1832851961242668</v>
       </c>
       <c r="T69">
-        <v>1.947264957826027</v>
+        <v>2.00057712422458</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.670449077218378</v>
+        <v>2.631177767259284</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09287566275976537</v>
+        <v>0.09275515146795721</v>
       </c>
       <c r="C70">
-        <v>163.3847820951502</v>
+        <v>160.3663506493601</v>
       </c>
       <c r="D70">
-        <v>419.0767820951502</v>
+        <v>420.1523506493601</v>
       </c>
       <c r="E70">
-        <v>112.092</v>
+        <v>116.186</v>
       </c>
       <c r="F70">
-        <v>278.392</v>
+        <v>282.486</v>
       </c>
       <c r="G70">
         <v>22.7</v>
@@ -7027,28 +7027,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M70">
-        <v>20.0163848</v>
+        <v>20.3107434</v>
       </c>
       <c r="N70">
-        <v>32.65028186666667</v>
+        <v>32.35592326666667</v>
       </c>
       <c r="O70">
-        <v>9.795084560000001</v>
+        <v>9.706776980000001</v>
       </c>
       <c r="P70">
-        <v>22.85519730666667</v>
+        <v>22.64914628666667</v>
       </c>
       <c r="Q70">
-        <v>52.85519730666667</v>
+        <v>52.64914628666667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1832851961242668</v>
+        <v>0.187185327315991</v>
       </c>
       <c r="T70">
-        <v>2.00057712422458</v>
+        <v>2.057328785229493</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.631177767259284</v>
+        <v>2.593044756139585</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09275515146795721</v>
+        <v>0.09263464017614906</v>
       </c>
       <c r="C71">
-        <v>160.3663506493601</v>
+        <v>157.3534543440303</v>
       </c>
       <c r="D71">
-        <v>420.1523506493601</v>
+        <v>421.2334543440303</v>
       </c>
       <c r="E71">
-        <v>116.186</v>
+        <v>120.28</v>
       </c>
       <c r="F71">
-        <v>282.486</v>
+        <v>286.58</v>
       </c>
       <c r="G71">
         <v>22.7</v>
@@ -7109,28 +7109,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M71">
-        <v>20.3107434</v>
+        <v>20.605102</v>
       </c>
       <c r="N71">
-        <v>32.35592326666667</v>
+        <v>32.06156466666667</v>
       </c>
       <c r="O71">
-        <v>9.706776980000001</v>
+        <v>9.6184694</v>
       </c>
       <c r="P71">
-        <v>22.64914628666667</v>
+        <v>22.44309526666667</v>
       </c>
       <c r="Q71">
-        <v>52.64914628666667</v>
+        <v>52.44309526666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.187185327315991</v>
+        <v>0.1913454672538302</v>
       </c>
       <c r="T71">
-        <v>2.057328785229493</v>
+        <v>2.117863890301399</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.593044756139585</v>
+        <v>2.556001259623304</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09263464017614906</v>
+        <v>0.09251412888434089</v>
       </c>
       <c r="C72">
-        <v>157.3534543440303</v>
+        <v>154.346136017181</v>
       </c>
       <c r="D72">
-        <v>421.2334543440303</v>
+        <v>422.320136017181</v>
       </c>
       <c r="E72">
-        <v>120.28</v>
+        <v>124.374</v>
       </c>
       <c r="F72">
-        <v>286.58</v>
+        <v>290.674</v>
       </c>
       <c r="G72">
         <v>22.7</v>
@@ -7191,28 +7191,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M72">
-        <v>20.605102</v>
+        <v>20.8994606</v>
       </c>
       <c r="N72">
-        <v>32.06156466666667</v>
+        <v>31.76720606666667</v>
       </c>
       <c r="O72">
-        <v>9.6184694</v>
+        <v>9.53016182</v>
       </c>
       <c r="P72">
-        <v>22.44309526666667</v>
+        <v>22.23704424666667</v>
       </c>
       <c r="Q72">
-        <v>52.44309526666667</v>
+        <v>52.23704424666667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1913454672538302</v>
+        <v>0.195792513394279</v>
       </c>
       <c r="T72">
-        <v>2.117863890301399</v>
+        <v>2.18257383020585</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.556001259623304</v>
+        <v>2.520001241882131</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09251412888434088</v>
+        <v>0.09435921759253273</v>
       </c>
       <c r="C73">
-        <v>154.3461360171811</v>
+        <v>134.2053759407344</v>
       </c>
       <c r="D73">
-        <v>422.3201360171811</v>
+        <v>406.2733759407344</v>
       </c>
       <c r="E73">
-        <v>124.374</v>
+        <v>128.468</v>
       </c>
       <c r="F73">
-        <v>290.674</v>
+        <v>294.768</v>
       </c>
       <c r="G73">
         <v>22.7</v>
@@ -7273,45 +7273,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M73">
-        <v>20.8994606</v>
+        <v>22.3434144</v>
       </c>
       <c r="N73">
-        <v>31.76720606666667</v>
+        <v>30.32325226666667</v>
       </c>
       <c r="O73">
-        <v>9.53016182</v>
+        <v>9.096975680000002</v>
       </c>
       <c r="P73">
-        <v>22.23704424666667</v>
+        <v>21.22627658666667</v>
       </c>
       <c r="Q73">
-        <v>52.23704424666667</v>
+        <v>51.22627658666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1957925133942789</v>
+        <v>0.2005572056876169</v>
       </c>
       <c r="T73">
-        <v>2.182573830205849</v>
+        <v>2.251905908674904</v>
       </c>
       <c r="U73">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.3</v>
       </c>
       <c r="W73">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.520001241882131</v>
+        <v>2.357144961097203</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09435921759253273</v>
+        <v>0.09426600630072457</v>
       </c>
       <c r="C74">
-        <v>134.2053759407344</v>
+        <v>130.8927332071805</v>
       </c>
       <c r="D74">
-        <v>406.2733759407344</v>
+        <v>407.0547332071805</v>
       </c>
       <c r="E74">
-        <v>128.468</v>
+        <v>132.562</v>
       </c>
       <c r="F74">
-        <v>294.768</v>
+        <v>298.862</v>
       </c>
       <c r="G74">
         <v>22.7</v>
@@ -7355,28 +7355,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M74">
-        <v>22.3434144</v>
+        <v>22.6537396</v>
       </c>
       <c r="N74">
-        <v>30.32325226666667</v>
+        <v>30.01292706666667</v>
       </c>
       <c r="O74">
-        <v>9.096975680000002</v>
+        <v>9.003878120000001</v>
       </c>
       <c r="P74">
-        <v>21.22627658666667</v>
+        <v>21.00904894666667</v>
       </c>
       <c r="Q74">
-        <v>51.22627658666667</v>
+        <v>51.00904894666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2005572056876169</v>
+        <v>0.2056748381508317</v>
       </c>
       <c r="T74">
-        <v>2.251905908674904</v>
+        <v>2.326373696660185</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.357144961097203</v>
+        <v>2.324855304095871</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09426600630072457</v>
+        <v>0.09417279500891641</v>
       </c>
       <c r="C75">
-        <v>130.8927332071805</v>
+        <v>127.5831017248954</v>
       </c>
       <c r="D75">
-        <v>407.0547332071805</v>
+        <v>407.8391017248953</v>
       </c>
       <c r="E75">
-        <v>132.562</v>
+        <v>136.6559999999999</v>
       </c>
       <c r="F75">
-        <v>298.862</v>
+        <v>302.956</v>
       </c>
       <c r="G75">
         <v>22.7</v>
@@ -7437,28 +7437,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M75">
-        <v>22.6537396</v>
+        <v>22.9640648</v>
       </c>
       <c r="N75">
-        <v>30.01292706666667</v>
+        <v>29.70260186666667</v>
       </c>
       <c r="O75">
-        <v>9.003878120000001</v>
+        <v>8.910780560000001</v>
       </c>
       <c r="P75">
-        <v>21.00904894666667</v>
+        <v>20.79182130666667</v>
       </c>
       <c r="Q75">
-        <v>51.00904894666667</v>
+        <v>50.79182130666667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2056748381508317</v>
+        <v>0.2111861346496785</v>
       </c>
       <c r="T75">
-        <v>2.326373696660185</v>
+        <v>2.40656977602895</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.324855304095871</v>
+        <v>2.293438340527008</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09417279500891641</v>
+        <v>0.09407958371710826</v>
       </c>
       <c r="C76">
-        <v>127.5831017248954</v>
+        <v>124.2764989349542</v>
       </c>
       <c r="D76">
-        <v>407.8391017248953</v>
+        <v>408.6264989349542</v>
       </c>
       <c r="E76">
-        <v>136.6559999999999</v>
+        <v>140.7499999999999</v>
       </c>
       <c r="F76">
-        <v>302.956</v>
+        <v>307.05</v>
       </c>
       <c r="G76">
         <v>22.7</v>
@@ -7519,28 +7519,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M76">
-        <v>22.9640648</v>
+        <v>23.27439</v>
       </c>
       <c r="N76">
-        <v>29.70260186666667</v>
+        <v>29.39227666666667</v>
       </c>
       <c r="O76">
-        <v>8.910780560000001</v>
+        <v>8.817683000000002</v>
       </c>
       <c r="P76">
-        <v>20.79182130666667</v>
+        <v>20.57459366666667</v>
       </c>
       <c r="Q76">
-        <v>50.79182130666667</v>
+        <v>50.57459366666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2111861346496785</v>
+        <v>0.217138334868433</v>
       </c>
       <c r="T76">
-        <v>2.40656977602895</v>
+        <v>2.493181541747215</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.293438340527008</v>
+        <v>2.262859162653315</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09407958371710826</v>
+        <v>0.09398637242530009</v>
       </c>
       <c r="C77">
-        <v>124.2764989349542</v>
+        <v>120.9729424133842</v>
       </c>
       <c r="D77">
-        <v>408.6264989349542</v>
+        <v>409.4169424133842</v>
       </c>
       <c r="E77">
-        <v>140.7499999999999</v>
+        <v>144.844</v>
       </c>
       <c r="F77">
-        <v>307.05</v>
+        <v>311.144</v>
       </c>
       <c r="G77">
         <v>22.7</v>
@@ -7601,28 +7601,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M77">
-        <v>23.27439</v>
+        <v>23.5847152</v>
       </c>
       <c r="N77">
-        <v>29.39227666666667</v>
+        <v>29.08195146666667</v>
       </c>
       <c r="O77">
-        <v>8.817683000000002</v>
+        <v>8.72458544</v>
       </c>
       <c r="P77">
-        <v>20.57459366666667</v>
+        <v>20.35736602666667</v>
       </c>
       <c r="Q77">
-        <v>50.57459366666667</v>
+        <v>50.35736602666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.217138334868433</v>
+        <v>0.2235865517720837</v>
       </c>
       <c r="T77">
-        <v>2.493181541747215</v>
+        <v>2.58701095460867</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.262859162653315</v>
+        <v>2.233084699986823</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09398637242530009</v>
+        <v>0.09389316113349191</v>
       </c>
       <c r="C78">
-        <v>120.9729424133842</v>
+        <v>117.6724498724713</v>
       </c>
       <c r="D78">
-        <v>409.4169424133842</v>
+        <v>410.2104498724713</v>
       </c>
       <c r="E78">
-        <v>144.844</v>
+        <v>148.938</v>
       </c>
       <c r="F78">
-        <v>311.144</v>
+        <v>315.238</v>
       </c>
       <c r="G78">
         <v>22.7</v>
@@ -7683,28 +7683,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M78">
-        <v>23.5847152</v>
+        <v>23.8950404</v>
       </c>
       <c r="N78">
-        <v>29.08195146666667</v>
+        <v>28.77162626666667</v>
       </c>
       <c r="O78">
-        <v>8.72458544</v>
+        <v>8.63148788</v>
       </c>
       <c r="P78">
-        <v>20.35736602666667</v>
+        <v>20.14013838666667</v>
       </c>
       <c r="Q78">
-        <v>50.35736602666667</v>
+        <v>50.14013838666667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2235865517720837</v>
+        <v>0.2305954831890953</v>
       </c>
       <c r="T78">
-        <v>2.58701095460867</v>
+        <v>2.688999446849381</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.233084699986823</v>
+        <v>2.204083599986994</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09389316113349191</v>
+        <v>0.09379994984168376</v>
       </c>
       <c r="C79">
-        <v>117.6724498724713</v>
+        <v>114.3750391620837</v>
       </c>
       <c r="D79">
-        <v>410.2104498724713</v>
+        <v>411.0070391620837</v>
       </c>
       <c r="E79">
-        <v>148.938</v>
+        <v>153.032</v>
       </c>
       <c r="F79">
-        <v>315.238</v>
+        <v>319.332</v>
       </c>
       <c r="G79">
         <v>22.7</v>
@@ -7765,28 +7765,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M79">
-        <v>23.8950404</v>
+        <v>24.2053656</v>
       </c>
       <c r="N79">
-        <v>28.77162626666667</v>
+        <v>28.46130106666667</v>
       </c>
       <c r="O79">
-        <v>8.63148788</v>
+        <v>8.538390320000001</v>
       </c>
       <c r="P79">
-        <v>20.14013838666667</v>
+        <v>19.92291074666667</v>
       </c>
       <c r="Q79">
-        <v>50.14013838666667</v>
+        <v>49.92291074666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2305954831890953</v>
+        <v>0.2382415901894716</v>
       </c>
       <c r="T79">
-        <v>2.688999446849381</v>
+        <v>2.800259620202884</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.204083599986994</v>
+        <v>2.175826117935879</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09379994984168376</v>
+        <v>0.0937067385498756</v>
       </c>
       <c r="C80">
-        <v>114.3750391620837</v>
+        <v>111.0807282710106</v>
       </c>
       <c r="D80">
-        <v>411.0070391620837</v>
+        <v>411.8067282710106</v>
       </c>
       <c r="E80">
-        <v>153.032</v>
+        <v>157.126</v>
       </c>
       <c r="F80">
-        <v>319.332</v>
+        <v>323.426</v>
       </c>
       <c r="G80">
         <v>22.7</v>
@@ -7847,28 +7847,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M80">
-        <v>24.2053656</v>
+        <v>24.5156908</v>
       </c>
       <c r="N80">
-        <v>28.46130106666667</v>
+        <v>28.15097586666667</v>
       </c>
       <c r="O80">
-        <v>8.538390320000001</v>
+        <v>8.445292760000001</v>
       </c>
       <c r="P80">
-        <v>19.92291074666667</v>
+        <v>19.70568310666667</v>
       </c>
       <c r="Q80">
-        <v>49.92291074666667</v>
+        <v>49.70568310666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2382415901894716</v>
+        <v>0.2466158978565505</v>
       </c>
       <c r="T80">
-        <v>2.800259620202884</v>
+        <v>2.922116000542436</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.175826117935879</v>
+        <v>2.148284015177197</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0937067385498756</v>
+        <v>0.09361352725806743</v>
       </c>
       <c r="C81">
-        <v>111.0807282710106</v>
+        <v>107.7895353283159</v>
       </c>
       <c r="D81">
-        <v>411.8067282710106</v>
+        <v>412.6095353283159</v>
       </c>
       <c r="E81">
-        <v>157.126</v>
+        <v>161.22</v>
       </c>
       <c r="F81">
-        <v>323.426</v>
+        <v>327.52</v>
       </c>
       <c r="G81">
         <v>22.7</v>
@@ -7929,28 +7929,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M81">
-        <v>24.5156908</v>
+        <v>24.826016</v>
       </c>
       <c r="N81">
-        <v>28.15097586666667</v>
+        <v>27.84065066666667</v>
       </c>
       <c r="O81">
-        <v>8.445292760000001</v>
+        <v>8.352195200000001</v>
       </c>
       <c r="P81">
-        <v>19.70568310666667</v>
+        <v>19.48845546666667</v>
       </c>
       <c r="Q81">
-        <v>49.70568310666667</v>
+        <v>49.48845546666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2466158978565505</v>
+        <v>0.2558276362903372</v>
       </c>
       <c r="T81">
-        <v>2.922116000542436</v>
+        <v>3.056158018915942</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.148284015177197</v>
+        <v>2.121430464987482</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09361352725806743</v>
+        <v>0.09352031596625929</v>
       </c>
       <c r="C82">
-        <v>107.7895353283159</v>
+        <v>104.5014786047079</v>
       </c>
       <c r="D82">
-        <v>412.6095353283159</v>
+        <v>413.4154786047079</v>
       </c>
       <c r="E82">
-        <v>161.22</v>
+        <v>165.314</v>
       </c>
       <c r="F82">
-        <v>327.52</v>
+        <v>331.614</v>
       </c>
       <c r="G82">
         <v>22.7</v>
@@ -8011,28 +8011,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M82">
-        <v>24.826016</v>
+        <v>25.1363412</v>
       </c>
       <c r="N82">
-        <v>27.84065066666667</v>
+        <v>27.53032546666667</v>
       </c>
       <c r="O82">
-        <v>8.352195200000001</v>
+        <v>8.25909764</v>
       </c>
       <c r="P82">
-        <v>19.48845546666667</v>
+        <v>19.27122782666667</v>
       </c>
       <c r="Q82">
-        <v>49.48845546666667</v>
+        <v>49.27122782666667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2558276362903372</v>
+        <v>0.2660090314013647</v>
       </c>
       <c r="T82">
-        <v>3.056158018915942</v>
+        <v>3.204309723434028</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.121430464987482</v>
+        <v>2.095239965419736</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09352031596625929</v>
+        <v>0.09342710467445112</v>
       </c>
       <c r="C83">
-        <v>104.5014786047079</v>
+        <v>101.2165765139266</v>
       </c>
       <c r="D83">
-        <v>413.4154786047079</v>
+        <v>414.2245765139266</v>
       </c>
       <c r="E83">
-        <v>165.314</v>
+        <v>169.408</v>
       </c>
       <c r="F83">
-        <v>331.614</v>
+        <v>335.708</v>
       </c>
       <c r="G83">
         <v>22.7</v>
@@ -8093,28 +8093,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M83">
-        <v>25.1363412</v>
+        <v>25.44666640000001</v>
       </c>
       <c r="N83">
-        <v>27.53032546666667</v>
+        <v>27.22000026666667</v>
       </c>
       <c r="O83">
-        <v>8.25909764</v>
+        <v>8.16600008</v>
       </c>
       <c r="P83">
-        <v>19.27122782666667</v>
+        <v>19.05400018666667</v>
       </c>
       <c r="Q83">
-        <v>49.27122782666667</v>
+        <v>49.05400018666667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2660090314013647</v>
+        <v>0.2773216926358396</v>
       </c>
       <c r="T83">
-        <v>3.204309723434028</v>
+        <v>3.368922728454124</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.095239965419736</v>
+        <v>2.069688258524372</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09342710467445112</v>
+        <v>0.09333389338264295</v>
       </c>
       <c r="C84">
-        <v>101.2165765139266</v>
+        <v>97.93484761414442</v>
       </c>
       <c r="D84">
-        <v>414.2245765139266</v>
+        <v>415.0368476141444</v>
       </c>
       <c r="E84">
-        <v>169.408</v>
+        <v>173.502</v>
       </c>
       <c r="F84">
-        <v>335.708</v>
+        <v>339.802</v>
       </c>
       <c r="G84">
         <v>22.7</v>
@@ -8175,28 +8175,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M84">
-        <v>25.44666640000001</v>
+        <v>25.7569916</v>
       </c>
       <c r="N84">
-        <v>27.22000026666667</v>
+        <v>26.90967506666667</v>
       </c>
       <c r="O84">
-        <v>8.16600008</v>
+        <v>8.07290252</v>
       </c>
       <c r="P84">
-        <v>19.05400018666667</v>
+        <v>18.83677254666667</v>
       </c>
       <c r="Q84">
-        <v>49.05400018666667</v>
+        <v>48.83677254666667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2773216926358396</v>
+        <v>0.2899652551920174</v>
       </c>
       <c r="T84">
-        <v>3.368922728454124</v>
+        <v>3.552901969358936</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.069688258524372</v>
+        <v>2.044752255409621</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09333389338264295</v>
+        <v>0.0932406820908348</v>
       </c>
       <c r="C85">
-        <v>97.93484761414442</v>
+        <v>94.65631060938597</v>
       </c>
       <c r="D85">
-        <v>415.0368476141444</v>
+        <v>415.852310609386</v>
       </c>
       <c r="E85">
-        <v>173.502</v>
+        <v>177.596</v>
       </c>
       <c r="F85">
-        <v>339.802</v>
+        <v>343.896</v>
       </c>
       <c r="G85">
         <v>22.7</v>
@@ -8257,28 +8257,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M85">
-        <v>25.7569916</v>
+        <v>26.0673168</v>
       </c>
       <c r="N85">
-        <v>26.90967506666667</v>
+        <v>26.59934986666667</v>
       </c>
       <c r="O85">
-        <v>8.07290252</v>
+        <v>7.97980496</v>
       </c>
       <c r="P85">
-        <v>18.83677254666667</v>
+        <v>18.61954490666667</v>
       </c>
       <c r="Q85">
-        <v>48.83677254666667</v>
+        <v>48.61954490666667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2899652551920174</v>
+        <v>0.3041892630677176</v>
       </c>
       <c r="T85">
-        <v>3.552901969358936</v>
+        <v>3.759878615376851</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.044752255409621</v>
+        <v>2.020409966654745</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0932406820908348</v>
+        <v>0.1015964707990266</v>
       </c>
       <c r="C86">
-        <v>94.65631060938603</v>
+        <v>28.28643560321967</v>
       </c>
       <c r="D86">
-        <v>415.852310609386</v>
+        <v>353.5764356032196</v>
       </c>
       <c r="E86">
-        <v>177.5959999999999</v>
+        <v>181.6899999999999</v>
       </c>
       <c r="F86">
-        <v>343.896</v>
+        <v>347.99</v>
       </c>
       <c r="G86">
         <v>22.7</v>
@@ -8339,45 +8339,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M86">
-        <v>26.0673168</v>
+        <v>31.3191</v>
       </c>
       <c r="N86">
-        <v>26.59934986666667</v>
+        <v>21.34756666666668</v>
       </c>
       <c r="O86">
-        <v>7.979804960000001</v>
+        <v>6.404270000000003</v>
       </c>
       <c r="P86">
-        <v>18.61954490666667</v>
+        <v>14.94329666666667</v>
       </c>
       <c r="Q86">
-        <v>48.61954490666667</v>
+        <v>44.94329666666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3041892630677174</v>
+        <v>0.3203098053268442</v>
       </c>
       <c r="T86">
-        <v>3.759878615376848</v>
+        <v>3.994452147530485</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.3</v>
       </c>
       <c r="W86">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.020409966654745</v>
+        <v>1.681614946363934</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1015964707990266</v>
+        <v>0.1016026595072185</v>
       </c>
       <c r="C87">
-        <v>28.28643560321967</v>
+        <v>24.15322275202624</v>
       </c>
       <c r="D87">
-        <v>353.5764356032196</v>
+        <v>353.5372227520263</v>
       </c>
       <c r="E87">
-        <v>181.6899999999999</v>
+        <v>185.784</v>
       </c>
       <c r="F87">
-        <v>347.99</v>
+        <v>352.084</v>
       </c>
       <c r="G87">
         <v>22.7</v>
@@ -8421,28 +8421,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M87">
-        <v>31.3191</v>
+        <v>31.68756</v>
       </c>
       <c r="N87">
-        <v>21.34756666666668</v>
+        <v>20.97910666666667</v>
       </c>
       <c r="O87">
-        <v>6.404270000000003</v>
+        <v>6.293732000000002</v>
       </c>
       <c r="P87">
-        <v>14.94329666666667</v>
+        <v>14.68537466666667</v>
       </c>
       <c r="Q87">
-        <v>44.94329666666667</v>
+        <v>44.68537466666668</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3203098053268442</v>
+        <v>0.3387332821944176</v>
       </c>
       <c r="T87">
-        <v>3.994452147530485</v>
+        <v>4.262536184277496</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.681614946363934</v>
+        <v>1.662061284196911</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1016026595072185</v>
+        <v>0.1016088482154103</v>
       </c>
       <c r="C88">
-        <v>24.15322275202624</v>
+        <v>20.02001859755023</v>
       </c>
       <c r="D88">
-        <v>353.5372227520263</v>
+        <v>353.4980185975502</v>
       </c>
       <c r="E88">
-        <v>185.784</v>
+        <v>189.878</v>
       </c>
       <c r="F88">
-        <v>352.084</v>
+        <v>356.178</v>
       </c>
       <c r="G88">
         <v>22.7</v>
@@ -8503,28 +8503,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M88">
-        <v>31.68756</v>
+        <v>32.05602</v>
       </c>
       <c r="N88">
-        <v>20.97910666666667</v>
+        <v>20.61064666666667</v>
       </c>
       <c r="O88">
-        <v>6.293732000000002</v>
+        <v>6.183194000000002</v>
       </c>
       <c r="P88">
-        <v>14.68537466666667</v>
+        <v>14.42745266666667</v>
       </c>
       <c r="Q88">
-        <v>44.68537466666668</v>
+        <v>44.42745266666667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3387332821944176</v>
+        <v>0.3599911401185408</v>
       </c>
       <c r="T88">
-        <v>4.262536184277496</v>
+        <v>4.571863918985589</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.662061284196911</v>
+        <v>1.642957131504993</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1016088482154103</v>
+        <v>0.1016150369236022</v>
       </c>
       <c r="C89">
-        <v>20.02001859755023</v>
+        <v>15.88682313689878</v>
       </c>
       <c r="D89">
-        <v>353.4980185975502</v>
+        <v>353.4588231368988</v>
       </c>
       <c r="E89">
-        <v>189.878</v>
+        <v>193.972</v>
       </c>
       <c r="F89">
-        <v>356.178</v>
+        <v>360.272</v>
       </c>
       <c r="G89">
         <v>22.7</v>
@@ -8585,28 +8585,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M89">
-        <v>32.05602</v>
+        <v>32.42448</v>
       </c>
       <c r="N89">
-        <v>20.61064666666667</v>
+        <v>20.24218666666668</v>
       </c>
       <c r="O89">
-        <v>6.183194000000002</v>
+        <v>6.072656000000003</v>
       </c>
       <c r="P89">
-        <v>14.42745266666667</v>
+        <v>14.16953066666667</v>
       </c>
       <c r="Q89">
-        <v>44.42745266666667</v>
+        <v>44.16953066666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3599911401185408</v>
+        <v>0.3847919743633513</v>
       </c>
       <c r="T89">
-        <v>4.571863918985589</v>
+        <v>4.932746276145028</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.642957131504993</v>
+        <v>1.624287164101527</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1016150369236022</v>
+        <v>0.101621225631794</v>
       </c>
       <c r="C90">
-        <v>15.88682313689878</v>
+        <v>11.75363636718055</v>
       </c>
       <c r="D90">
-        <v>353.4588231368988</v>
+        <v>353.4196363671805</v>
       </c>
       <c r="E90">
-        <v>193.972</v>
+        <v>198.066</v>
       </c>
       <c r="F90">
-        <v>360.272</v>
+        <v>364.366</v>
       </c>
       <c r="G90">
         <v>22.7</v>
@@ -8667,28 +8667,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M90">
-        <v>32.42448</v>
+        <v>32.79293999999999</v>
       </c>
       <c r="N90">
-        <v>20.24218666666668</v>
+        <v>19.87372666666668</v>
       </c>
       <c r="O90">
-        <v>6.072656000000003</v>
+        <v>5.962118000000003</v>
       </c>
       <c r="P90">
-        <v>14.16953066666667</v>
+        <v>13.91160866666667</v>
       </c>
       <c r="Q90">
-        <v>44.16953066666667</v>
+        <v>43.91160866666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3847919743633513</v>
+        <v>0.4141020511981272</v>
       </c>
       <c r="T90">
-        <v>4.932746276145028</v>
+        <v>5.359243607333458</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.624287164101527</v>
+        <v>1.606036746527352</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.101621225631794</v>
+        <v>0.1016274143399858</v>
       </c>
       <c r="C91">
-        <v>11.75363636718055</v>
+        <v>7.620458285505151</v>
       </c>
       <c r="D91">
-        <v>353.4196363671805</v>
+        <v>353.3804582855051</v>
       </c>
       <c r="E91">
-        <v>198.066</v>
+        <v>202.16</v>
       </c>
       <c r="F91">
-        <v>364.366</v>
+        <v>368.46</v>
       </c>
       <c r="G91">
         <v>22.7</v>
@@ -8749,28 +8749,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M91">
-        <v>32.79293999999999</v>
+        <v>33.1614</v>
       </c>
       <c r="N91">
-        <v>19.87372666666668</v>
+        <v>19.50526666666667</v>
       </c>
       <c r="O91">
-        <v>5.962118000000003</v>
+        <v>5.851580000000001</v>
       </c>
       <c r="P91">
-        <v>13.91160866666667</v>
+        <v>13.65368666666667</v>
       </c>
       <c r="Q91">
-        <v>43.91160866666667</v>
+        <v>43.65368666666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4141020511981272</v>
+        <v>0.4492741433998583</v>
       </c>
       <c r="T91">
-        <v>5.359243607333458</v>
+        <v>5.871040404759572</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.606036746527352</v>
+        <v>1.58819189378816</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1016274143399858</v>
+        <v>0.1016336030481777</v>
       </c>
       <c r="C92">
-        <v>7.620458285505151</v>
+        <v>3.487288888983471</v>
       </c>
       <c r="D92">
-        <v>353.3804582855051</v>
+        <v>353.3412888889835</v>
       </c>
       <c r="E92">
-        <v>202.16</v>
+        <v>206.254</v>
       </c>
       <c r="F92">
-        <v>368.46</v>
+        <v>372.554</v>
       </c>
       <c r="G92">
         <v>22.7</v>
@@ -8831,28 +8831,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M92">
-        <v>33.1614</v>
+        <v>33.52986</v>
       </c>
       <c r="N92">
-        <v>19.50526666666667</v>
+        <v>19.13680666666667</v>
       </c>
       <c r="O92">
-        <v>5.851580000000001</v>
+        <v>5.741042000000001</v>
       </c>
       <c r="P92">
-        <v>13.65368666666667</v>
+        <v>13.39576466666667</v>
       </c>
       <c r="Q92">
-        <v>43.65368666666667</v>
+        <v>43.39576466666667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4492741433998583</v>
+        <v>0.492262256090863</v>
       </c>
       <c r="T92">
-        <v>5.871040404759572</v>
+        <v>6.496569823835936</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.58819189378816</v>
+        <v>1.570739235614663</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1016336030481777</v>
+        <v>0.1016397917563695</v>
       </c>
       <c r="C93">
-        <v>3.487288888983471</v>
+        <v>-0.6458718252721383</v>
       </c>
       <c r="D93">
-        <v>353.3412888889835</v>
+        <v>353.3021281747278</v>
       </c>
       <c r="E93">
-        <v>206.254</v>
+        <v>210.348</v>
       </c>
       <c r="F93">
-        <v>372.554</v>
+        <v>376.648</v>
       </c>
       <c r="G93">
         <v>22.7</v>
@@ -8913,28 +8913,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M93">
-        <v>33.52986</v>
+        <v>33.89832</v>
       </c>
       <c r="N93">
-        <v>19.13680666666667</v>
+        <v>18.76834666666667</v>
       </c>
       <c r="O93">
-        <v>5.741042000000001</v>
+        <v>5.630504000000002</v>
       </c>
       <c r="P93">
-        <v>13.39576466666667</v>
+        <v>13.13784266666667</v>
       </c>
       <c r="Q93">
-        <v>43.39576466666667</v>
+        <v>43.13784266666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.492262256090863</v>
+        <v>0.545997396954619</v>
       </c>
       <c r="T93">
-        <v>6.496569823835936</v>
+        <v>7.278481597681391</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.570739235614663</v>
+        <v>1.553665983053634</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1016397917563695</v>
+        <v>0.1016459804645613</v>
       </c>
       <c r="C94">
-        <v>-0.6458718252721383</v>
+        <v>-4.779023860148072</v>
       </c>
       <c r="D94">
-        <v>353.3021281747278</v>
+        <v>353.262976139852</v>
       </c>
       <c r="E94">
-        <v>210.348</v>
+        <v>214.442</v>
       </c>
       <c r="F94">
-        <v>376.648</v>
+        <v>380.742</v>
       </c>
       <c r="G94">
         <v>22.7</v>
@@ -8995,28 +8995,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M94">
-        <v>33.89832</v>
+        <v>34.26678</v>
       </c>
       <c r="N94">
-        <v>18.76834666666667</v>
+        <v>18.39988666666667</v>
       </c>
       <c r="O94">
-        <v>5.630504000000002</v>
+        <v>5.519966000000002</v>
       </c>
       <c r="P94">
-        <v>13.13784266666667</v>
+        <v>12.87992066666667</v>
       </c>
       <c r="Q94">
-        <v>43.13784266666667</v>
+        <v>42.87992066666667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.545997396954619</v>
+        <v>0.6150854352080195</v>
       </c>
       <c r="T94">
-        <v>7.278481597681391</v>
+        <v>8.283796735482689</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.553665983053634</v>
+        <v>1.536959897214348</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1016459804645613</v>
+        <v>0.1016521691727532</v>
       </c>
       <c r="C95">
-        <v>-4.779023860148072</v>
+        <v>-8.912167218529589</v>
       </c>
       <c r="D95">
-        <v>353.262976139852</v>
+        <v>353.2238327814704</v>
       </c>
       <c r="E95">
-        <v>214.442</v>
+        <v>218.536</v>
       </c>
       <c r="F95">
-        <v>380.742</v>
+        <v>384.836</v>
       </c>
       <c r="G95">
         <v>22.7</v>
@@ -9077,28 +9077,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M95">
-        <v>34.26678</v>
+        <v>34.63524</v>
       </c>
       <c r="N95">
-        <v>18.39988666666667</v>
+        <v>18.03142666666667</v>
       </c>
       <c r="O95">
-        <v>5.519966000000002</v>
+        <v>5.409428</v>
       </c>
       <c r="P95">
-        <v>12.87992066666667</v>
+        <v>12.62199866666667</v>
       </c>
       <c r="Q95">
-        <v>42.87992066666667</v>
+        <v>42.62199866666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6150854352080195</v>
+        <v>0.707202819545887</v>
       </c>
       <c r="T95">
-        <v>8.283796735482689</v>
+        <v>9.624216919217755</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.536959897214348</v>
+        <v>1.52060926000994</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1016521691727532</v>
+        <v>0.101658357880945</v>
       </c>
       <c r="C96">
-        <v>-8.912167218529589</v>
+        <v>-13.04530190330036</v>
       </c>
       <c r="D96">
-        <v>353.2238327814704</v>
+        <v>353.1846980966997</v>
       </c>
       <c r="E96">
-        <v>218.536</v>
+        <v>222.63</v>
       </c>
       <c r="F96">
-        <v>384.836</v>
+        <v>388.93</v>
       </c>
       <c r="G96">
         <v>22.7</v>
@@ -9159,28 +9159,28 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M96">
-        <v>34.63524</v>
+        <v>35.0037</v>
       </c>
       <c r="N96">
-        <v>18.03142666666667</v>
+        <v>17.66296666666667</v>
       </c>
       <c r="O96">
-        <v>5.409428</v>
+        <v>5.298890000000001</v>
       </c>
       <c r="P96">
-        <v>12.62199866666667</v>
+        <v>12.36407666666667</v>
       </c>
       <c r="Q96">
-        <v>42.62199866666667</v>
+        <v>42.36407666666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.707202819545887</v>
+        <v>0.8361671576189015</v>
       </c>
       <c r="T96">
-        <v>9.624216919217755</v>
+        <v>11.50080517644685</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.52060926000994</v>
+        <v>1.504602846746677</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.101658357880945</v>
+        <v>0.1449070187325718</v>
       </c>
       <c r="C97">
-        <v>-13.04530190330036</v>
+        <v>-171.2632521674632</v>
       </c>
       <c r="D97">
-        <v>353.1846980966997</v>
+        <v>199.0607478325368</v>
       </c>
       <c r="E97">
-        <v>222.63</v>
+        <v>226.724</v>
       </c>
       <c r="F97">
-        <v>388.93</v>
+        <v>393.024</v>
       </c>
       <c r="G97">
         <v>22.7</v>
@@ -9241,45 +9241,45 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M97">
-        <v>35.0037</v>
+        <v>57.6959232</v>
       </c>
       <c r="N97">
-        <v>17.66296666666667</v>
+        <v>-5.029256533333331</v>
       </c>
       <c r="O97">
-        <v>5.298890000000001</v>
+        <v>-1.508776959999999</v>
       </c>
       <c r="P97">
-        <v>12.36407666666667</v>
+        <v>-3.520479573333332</v>
       </c>
       <c r="Q97">
-        <v>42.36407666666667</v>
+        <v>26.47952042666667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8361671576189015</v>
+        <v>1.064302043790602</v>
       </c>
       <c r="T97">
-        <v>11.50080517644685</v>
+        <v>14.82044574414958</v>
       </c>
       <c r="U97">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.3</v>
+        <v>0.2738495048468173</v>
       </c>
       <c r="W97">
-        <v>0.063</v>
+        <v>0.1065988926884872</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.504602846746677</v>
+        <v>0.9128316828227244</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1449070187325717</v>
+        <v>0.1459170187325717</v>
       </c>
       <c r="C98">
-        <v>-171.263252167463</v>
+        <v>-177.3654157929493</v>
       </c>
       <c r="D98">
-        <v>199.0607478325369</v>
+        <v>197.0525842070507</v>
       </c>
       <c r="E98">
-        <v>226.7239999999999</v>
+        <v>230.818</v>
       </c>
       <c r="F98">
-        <v>393.0239999999999</v>
+        <v>397.118</v>
       </c>
       <c r="G98">
         <v>22.7</v>
@@ -9323,37 +9323,37 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M98">
-        <v>57.6959232</v>
+        <v>58.29692240000001</v>
       </c>
       <c r="N98">
-        <v>-5.029256533333324</v>
+        <v>-5.630255733333335</v>
       </c>
       <c r="O98">
-        <v>-1.508776959999997</v>
+        <v>-1.689076720000001</v>
       </c>
       <c r="P98">
-        <v>-3.520479573333327</v>
+        <v>-3.941179013333335</v>
       </c>
       <c r="Q98">
-        <v>26.47952042666667</v>
+        <v>26.05882098666666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.064302043790599</v>
+        <v>1.403802725054132</v>
       </c>
       <c r="T98">
-        <v>14.82044574414953</v>
+        <v>19.76059432553272</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2738495048468174</v>
+        <v>0.2710263140752006</v>
       </c>
       <c r="W98">
-        <v>0.1065988926884872</v>
+        <v>0.1070133370937606</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9128316828227245</v>
+        <v>0.9034210469173355</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1459170187325717</v>
+        <v>0.1469270187325717</v>
       </c>
       <c r="C99">
-        <v>-177.3654157929493</v>
+        <v>-183.4274665922656</v>
       </c>
       <c r="D99">
-        <v>197.0525842070507</v>
+        <v>195.0845334077344</v>
       </c>
       <c r="E99">
-        <v>230.818</v>
+        <v>234.912</v>
       </c>
       <c r="F99">
-        <v>397.118</v>
+        <v>401.212</v>
       </c>
       <c r="G99">
         <v>22.7</v>
@@ -9405,37 +9405,37 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M99">
-        <v>58.29692240000001</v>
+        <v>58.8979216</v>
       </c>
       <c r="N99">
-        <v>-5.630255733333335</v>
+        <v>-6.231254933333332</v>
       </c>
       <c r="O99">
-        <v>-1.689076720000001</v>
+        <v>-1.86937648</v>
       </c>
       <c r="P99">
-        <v>-3.941179013333335</v>
+        <v>-4.361878453333333</v>
       </c>
       <c r="Q99">
-        <v>26.05882098666666</v>
+        <v>25.63812154666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.403802725054132</v>
+        <v>2.082804087581198</v>
       </c>
       <c r="T99">
-        <v>19.76059432553272</v>
+        <v>29.64089148829907</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2710263140752006</v>
+        <v>0.2682607394417802</v>
       </c>
       <c r="W99">
-        <v>0.1070133370937606</v>
+        <v>0.1074193234499467</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9034210469173355</v>
+        <v>0.8942024648059341</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1469270187325717</v>
+        <v>0.1479370187325717</v>
       </c>
       <c r="C100">
-        <v>-183.4274665922656</v>
+        <v>-189.4505945537711</v>
       </c>
       <c r="D100">
-        <v>195.0845334077344</v>
+        <v>193.1554054462289</v>
       </c>
       <c r="E100">
-        <v>234.912</v>
+        <v>239.006</v>
       </c>
       <c r="F100">
-        <v>401.212</v>
+        <v>405.306</v>
       </c>
       <c r="G100">
         <v>22.7</v>
@@ -9487,37 +9487,37 @@
         <v>52.66666666666667</v>
       </c>
       <c r="M100">
-        <v>58.8979216</v>
+        <v>59.4989208</v>
       </c>
       <c r="N100">
-        <v>-6.231254933333332</v>
+        <v>-6.832254133333329</v>
       </c>
       <c r="O100">
-        <v>-1.86937648</v>
+        <v>-2.049676239999999</v>
       </c>
       <c r="P100">
-        <v>-4.361878453333333</v>
+        <v>-4.782577893333331</v>
       </c>
       <c r="Q100">
-        <v>25.63812154666667</v>
+        <v>25.21742210666667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.082804087581198</v>
+        <v>4.119808175162395</v>
       </c>
       <c r="T100">
-        <v>29.64089148829907</v>
+        <v>59.28178297659814</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2682607394417802</v>
+        <v>0.2655510350029744</v>
       </c>
       <c r="W100">
-        <v>0.1074193234499467</v>
+        <v>0.1078171080615634</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8942024648059341</v>
+        <v>0.8851701166765813</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1479370187325717</v>
-      </c>
-      <c r="C101">
-        <v>-189.4505945537711</v>
-      </c>
-      <c r="D101">
-        <v>193.1554054462289</v>
-      </c>
-      <c r="E101">
-        <v>239.006</v>
-      </c>
-      <c r="F101">
-        <v>405.306</v>
-      </c>
-      <c r="G101">
-        <v>22.7</v>
-      </c>
-      <c r="H101">
-        <v>243.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>82.66666666666667</v>
-      </c>
-      <c r="K101">
-        <v>30</v>
-      </c>
-      <c r="L101">
-        <v>52.66666666666667</v>
-      </c>
-      <c r="M101">
-        <v>59.4989208</v>
-      </c>
-      <c r="N101">
-        <v>-6.832254133333329</v>
-      </c>
-      <c r="O101">
-        <v>-2.049676239999999</v>
-      </c>
-      <c r="P101">
-        <v>-4.782577893333331</v>
-      </c>
-      <c r="Q101">
-        <v>25.21742210666667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.119808175162395</v>
-      </c>
-      <c r="T101">
-        <v>59.28178297659814</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2655510350029744</v>
-      </c>
-      <c r="W101">
-        <v>0.1078171080615634</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8851701166765813</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
